--- a/materias/SIM/entregables/TPI/subte/04-resultados-corridas.xlsx
+++ b/materias/SIM/entregables/TPI/subte/04-resultados-corridas.xlsx
@@ -1236,7 +1236,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Tiempo de disipación</t>
+          <t>Tiempo de drenaje final</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1862,17 +1862,17 @@
       </c>
       <c r="AD7" s="5" t="inlineStr">
         <is>
-          <t>E0 Tiempo de disipación</t>
+          <t>E0 Tiempo de drenaje final</t>
         </is>
       </c>
       <c r="AE7" s="5" t="inlineStr">
         <is>
-          <t>E1 Tiempo de disipación</t>
+          <t>E1 Tiempo de drenaje final</t>
         </is>
       </c>
       <c r="AF7" s="5" t="inlineStr">
         <is>
-          <t>Diferencia Tiempo de disipación</t>
+          <t>Diferencia Tiempo de drenaje final</t>
         </is>
       </c>
       <c r="AG7" s="5" t="inlineStr">

--- a/materias/SIM/entregables/TPI/subte/04-resultados-corridas.xlsx
+++ b/materias/SIM/entregables/TPI/subte/04-resultados-corridas.xlsx
@@ -1627,7 +1627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AU67"/>
+  <dimension ref="A2:AU68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1958,92 +1958,152 @@
       <c r="B8" s="9" t="n">
         <v>20260923</v>
       </c>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
+      <c r="C8" s="10" t="n">
+        <v>18416</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>18416</v>
+      </c>
       <c r="E8" s="11">
         <f>IF(OR(C8="",D8=""),"",D8-C8)</f>
         <v/>
       </c>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
+      <c r="F8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H8" s="11">
         <f>IF(OR(F8="",G8=""),"",G8-F8)</f>
         <v/>
       </c>
-      <c r="I8" s="10" t="n"/>
-      <c r="J8" s="10" t="n"/>
+      <c r="I8" s="10" t="n">
+        <v>18209</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>18212</v>
+      </c>
       <c r="K8" s="11">
         <f>IF(OR(I8="",J8=""),"",J8-I8)</f>
         <v/>
       </c>
-      <c r="L8" s="10" t="n"/>
-      <c r="M8" s="10" t="n"/>
+      <c r="L8" s="10" t="n">
+        <v>18416</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>18416</v>
+      </c>
       <c r="N8" s="11">
         <f>IF(OR(L8="",M8=""),"",M8-L8)</f>
         <v/>
       </c>
-      <c r="O8" s="10" t="n"/>
-      <c r="P8" s="10" t="n"/>
+      <c r="O8" s="10" t="n">
+        <v>10.746959</v>
+      </c>
+      <c r="P8" s="10" t="n">
+        <v>7.300103</v>
+      </c>
       <c r="Q8" s="11">
         <f>IF(OR(O8="",P8=""),"",P8-O8)</f>
         <v/>
       </c>
-      <c r="R8" s="10" t="n"/>
-      <c r="S8" s="10" t="n"/>
+      <c r="R8" s="10" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="S8" s="10" t="n">
+        <v>18.3</v>
+      </c>
       <c r="T8" s="11">
         <f>IF(OR(R8="",S8=""),"",S8-R8)</f>
         <v/>
       </c>
-      <c r="U8" s="12" t="n"/>
-      <c r="V8" s="12" t="n"/>
+      <c r="U8" s="12" t="n">
+        <v>0.08096200000000001</v>
+      </c>
+      <c r="V8" s="12" t="n">
+        <v>0.018462</v>
+      </c>
       <c r="W8" s="13">
         <f>IF(OR(U8="",V8=""),"",V8-U8)</f>
         <v/>
       </c>
-      <c r="X8" s="10" t="n"/>
-      <c r="Y8" s="10" t="n"/>
+      <c r="X8" s="10" t="n">
+        <v>21.931933</v>
+      </c>
+      <c r="Y8" s="10" t="n">
+        <v>14.893867</v>
+      </c>
       <c r="Z8" s="11">
         <f>IF(OR(X8="",Y8=""),"",Y8-X8)</f>
         <v/>
       </c>
-      <c r="AA8" s="10" t="n"/>
-      <c r="AB8" s="10" t="n"/>
+      <c r="AA8" s="10" t="n">
+        <v>224</v>
+      </c>
+      <c r="AB8" s="10" t="n">
+        <v>168</v>
+      </c>
       <c r="AC8" s="11">
         <f>IF(OR(AA8="",AB8=""),"",AB8-AA8)</f>
         <v/>
       </c>
-      <c r="AD8" s="10" t="n"/>
-      <c r="AE8" s="10" t="n"/>
+      <c r="AD8" s="10" t="n">
+        <v>65.180786</v>
+      </c>
+      <c r="AE8" s="10" t="n">
+        <v>65.78078600000001</v>
+      </c>
       <c r="AF8" s="11">
         <f>IF(OR(AD8="",AE8=""),"",AE8-AD8)</f>
         <v/>
       </c>
-      <c r="AG8" s="12" t="n"/>
-      <c r="AH8" s="12" t="n"/>
+      <c r="AG8" s="12" t="n">
+        <v>0.260496</v>
+      </c>
+      <c r="AH8" s="12" t="n">
+        <v>0.236869</v>
+      </c>
       <c r="AI8" s="13">
         <f>IF(OR(AG8="",AH8=""),"",AH8-AG8)</f>
         <v/>
       </c>
-      <c r="AJ8" s="12" t="n"/>
-      <c r="AK8" s="12" t="n"/>
+      <c r="AJ8" s="12" t="n">
+        <v>0.046893</v>
+      </c>
+      <c r="AK8" s="12" t="n">
+        <v>0.050486</v>
+      </c>
       <c r="AL8" s="13">
         <f>IF(OR(AJ8="",AK8=""),"",AK8-AJ8)</f>
         <v/>
       </c>
-      <c r="AM8" s="10" t="n"/>
-      <c r="AN8" s="10" t="n"/>
+      <c r="AM8" s="10" t="n">
+        <v>4360</v>
+      </c>
+      <c r="AN8" s="10" t="n">
+        <v>4360</v>
+      </c>
       <c r="AO8" s="11">
         <f>IF(OR(AM8="",AN8=""),"",AN8-AM8)</f>
         <v/>
       </c>
-      <c r="AP8" s="10" t="n"/>
-      <c r="AQ8" s="10" t="n"/>
+      <c r="AP8" s="10" t="n">
+        <v>15.582661</v>
+      </c>
+      <c r="AQ8" s="10" t="n">
+        <v>10.343807</v>
+      </c>
       <c r="AR8" s="11">
         <f>IF(OR(AP8="",AQ8=""),"",AQ8-AP8)</f>
         <v/>
       </c>
-      <c r="AS8" s="10" t="n"/>
-      <c r="AT8" s="10" t="n"/>
+      <c r="AS8" s="10" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="AT8" s="10" t="n">
+        <v>24.9</v>
+      </c>
       <c r="AU8" s="11">
         <f>IF(OR(AS8="",AT8=""),"",AT8-AS8)</f>
         <v/>
@@ -2056,92 +2116,152 @@
       <c r="B9" s="9" t="n">
         <v>20260924</v>
       </c>
-      <c r="C9" s="10" t="n"/>
-      <c r="D9" s="10" t="n"/>
+      <c r="C9" s="10" t="n">
+        <v>18401</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>18401</v>
+      </c>
       <c r="E9" s="11">
         <f>IF(OR(C9="",D9=""),"",D9-C9)</f>
         <v/>
       </c>
-      <c r="F9" s="10" t="n"/>
-      <c r="G9" s="10" t="n"/>
+      <c r="F9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H9" s="11">
         <f>IF(OR(F9="",G9=""),"",G9-F9)</f>
         <v/>
       </c>
-      <c r="I9" s="10" t="n"/>
-      <c r="J9" s="10" t="n"/>
+      <c r="I9" s="10" t="n">
+        <v>18193</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>18191</v>
+      </c>
       <c r="K9" s="11">
         <f>IF(OR(I9="",J9=""),"",J9-I9)</f>
         <v/>
       </c>
-      <c r="L9" s="10" t="n"/>
-      <c r="M9" s="10" t="n"/>
+      <c r="L9" s="10" t="n">
+        <v>18401</v>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>18401</v>
+      </c>
       <c r="N9" s="11">
         <f>IF(OR(L9="",M9=""),"",M9-L9)</f>
         <v/>
       </c>
-      <c r="O9" s="10" t="n"/>
-      <c r="P9" s="10" t="n"/>
+      <c r="O9" s="10" t="n">
+        <v>10.690799</v>
+      </c>
+      <c r="P9" s="10" t="n">
+        <v>7.312983</v>
+      </c>
       <c r="Q9" s="11">
         <f>IF(OR(O9="",P9=""),"",P9-O9)</f>
         <v/>
       </c>
-      <c r="R9" s="10" t="n"/>
-      <c r="S9" s="10" t="n"/>
+      <c r="R9" s="10" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="S9" s="10" t="n">
+        <v>18</v>
+      </c>
       <c r="T9" s="11">
         <f>IF(OR(R9="",S9=""),"",S9-R9)</f>
         <v/>
       </c>
-      <c r="U9" s="12" t="n"/>
-      <c r="V9" s="12" t="n"/>
+      <c r="U9" s="12" t="n">
+        <v>0.079126</v>
+      </c>
+      <c r="V9" s="12" t="n">
+        <v>0.018695</v>
+      </c>
       <c r="W9" s="13">
         <f>IF(OR(U9="",V9=""),"",V9-U9)</f>
         <v/>
       </c>
-      <c r="X9" s="10" t="n"/>
-      <c r="Y9" s="10" t="n"/>
+      <c r="X9" s="10" t="n">
+        <v>21.7905</v>
+      </c>
+      <c r="Y9" s="10" t="n">
+        <v>14.896233</v>
+      </c>
       <c r="Z9" s="11">
         <f>IF(OR(X9="",Y9=""),"",Y9-X9)</f>
         <v/>
       </c>
-      <c r="AA9" s="10" t="n"/>
-      <c r="AB9" s="10" t="n"/>
+      <c r="AA9" s="10" t="n">
+        <v>226</v>
+      </c>
+      <c r="AB9" s="10" t="n">
+        <v>170</v>
+      </c>
       <c r="AC9" s="11">
         <f>IF(OR(AA9="",AB9=""),"",AB9-AA9)</f>
         <v/>
       </c>
-      <c r="AD9" s="10" t="n"/>
-      <c r="AE9" s="10" t="n"/>
+      <c r="AD9" s="10" t="n">
+        <v>62.780786</v>
+      </c>
+      <c r="AE9" s="10" t="n">
+        <v>66.680786</v>
+      </c>
       <c r="AF9" s="11">
         <f>IF(OR(AD9="",AE9=""),"",AE9-AD9)</f>
         <v/>
       </c>
-      <c r="AG9" s="12" t="n"/>
-      <c r="AH9" s="12" t="n"/>
+      <c r="AG9" s="12" t="n">
+        <v>0.260838</v>
+      </c>
+      <c r="AH9" s="12" t="n">
+        <v>0.237166</v>
+      </c>
       <c r="AI9" s="13">
         <f>IF(OR(AG9="",AH9=""),"",AH9-AG9)</f>
         <v/>
       </c>
-      <c r="AJ9" s="12" t="n"/>
-      <c r="AK9" s="12" t="n"/>
+      <c r="AJ9" s="12" t="n">
+        <v>0.047257</v>
+      </c>
+      <c r="AK9" s="12" t="n">
+        <v>0.051511</v>
+      </c>
       <c r="AL9" s="13">
         <f>IF(OR(AJ9="",AK9=""),"",AK9-AJ9)</f>
         <v/>
       </c>
-      <c r="AM9" s="10" t="n"/>
-      <c r="AN9" s="10" t="n"/>
+      <c r="AM9" s="10" t="n">
+        <v>4337</v>
+      </c>
+      <c r="AN9" s="10" t="n">
+        <v>4337</v>
+      </c>
       <c r="AO9" s="11">
         <f>IF(OR(AM9="",AN9=""),"",AN9-AM9)</f>
         <v/>
       </c>
-      <c r="AP9" s="10" t="n"/>
-      <c r="AQ9" s="10" t="n"/>
+      <c r="AP9" s="10" t="n">
+        <v>16.004658</v>
+      </c>
+      <c r="AQ9" s="10" t="n">
+        <v>10.584113</v>
+      </c>
       <c r="AR9" s="11">
         <f>IF(OR(AP9="",AQ9=""),"",AQ9-AP9)</f>
         <v/>
       </c>
-      <c r="AS9" s="10" t="n"/>
-      <c r="AT9" s="10" t="n"/>
+      <c r="AS9" s="10" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="AT9" s="10" t="n">
+        <v>24.9</v>
+      </c>
       <c r="AU9" s="11">
         <f>IF(OR(AS9="",AT9=""),"",AT9-AS9)</f>
         <v/>
@@ -2154,92 +2274,152 @@
       <c r="B10" s="9" t="n">
         <v>20260925</v>
       </c>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="10" t="n"/>
+      <c r="C10" s="10" t="n">
+        <v>18331</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>18331</v>
+      </c>
       <c r="E10" s="11">
         <f>IF(OR(C10="",D10=""),"",D10-C10)</f>
         <v/>
       </c>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
+      <c r="F10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H10" s="11">
         <f>IF(OR(F10="",G10=""),"",G10-F10)</f>
         <v/>
       </c>
-      <c r="I10" s="10" t="n"/>
-      <c r="J10" s="10" t="n"/>
+      <c r="I10" s="10" t="n">
+        <v>18126</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>18128</v>
+      </c>
       <c r="K10" s="11">
         <f>IF(OR(I10="",J10=""),"",J10-I10)</f>
         <v/>
       </c>
-      <c r="L10" s="10" t="n"/>
-      <c r="M10" s="10" t="n"/>
+      <c r="L10" s="10" t="n">
+        <v>18331</v>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>18331</v>
+      </c>
       <c r="N10" s="11">
         <f>IF(OR(L10="",M10=""),"",M10-L10)</f>
         <v/>
       </c>
-      <c r="O10" s="10" t="n"/>
-      <c r="P10" s="10" t="n"/>
+      <c r="O10" s="10" t="n">
+        <v>10.968469</v>
+      </c>
+      <c r="P10" s="10" t="n">
+        <v>7.525056</v>
+      </c>
       <c r="Q10" s="11">
         <f>IF(OR(O10="",P10=""),"",P10-O10)</f>
         <v/>
       </c>
-      <c r="R10" s="10" t="n"/>
-      <c r="S10" s="10" t="n"/>
+      <c r="R10" s="10" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="S10" s="10" t="n">
+        <v>18.6</v>
+      </c>
       <c r="T10" s="11">
         <f>IF(OR(R10="",S10=""),"",S10-R10)</f>
         <v/>
       </c>
-      <c r="U10" s="12" t="n"/>
-      <c r="V10" s="12" t="n"/>
+      <c r="U10" s="12" t="n">
+        <v>0.08701100000000001</v>
+      </c>
+      <c r="V10" s="12" t="n">
+        <v>0.024767</v>
+      </c>
       <c r="W10" s="13">
         <f>IF(OR(U10="",V10=""),"",V10-U10)</f>
         <v/>
       </c>
-      <c r="X10" s="10" t="n"/>
-      <c r="Y10" s="10" t="n"/>
+      <c r="X10" s="10" t="n">
+        <v>22.265967</v>
+      </c>
+      <c r="Y10" s="10" t="n">
+        <v>15.273867</v>
+      </c>
       <c r="Z10" s="11">
         <f>IF(OR(X10="",Y10=""),"",Y10-X10)</f>
         <v/>
       </c>
-      <c r="AA10" s="10" t="n"/>
-      <c r="AB10" s="10" t="n"/>
+      <c r="AA10" s="10" t="n">
+        <v>231</v>
+      </c>
+      <c r="AB10" s="10" t="n">
+        <v>168</v>
+      </c>
       <c r="AC10" s="11">
         <f>IF(OR(AA10="",AB10=""),"",AB10-AA10)</f>
         <v/>
       </c>
-      <c r="AD10" s="10" t="n"/>
-      <c r="AE10" s="10" t="n"/>
+      <c r="AD10" s="10" t="n">
+        <v>67.880786</v>
+      </c>
+      <c r="AE10" s="10" t="n">
+        <v>67.28078600000001</v>
+      </c>
       <c r="AF10" s="11">
         <f>IF(OR(AD10="",AE10=""),"",AE10-AD10)</f>
         <v/>
       </c>
-      <c r="AG10" s="12" t="n"/>
-      <c r="AH10" s="12" t="n"/>
+      <c r="AG10" s="12" t="n">
+        <v>0.260075</v>
+      </c>
+      <c r="AH10" s="12" t="n">
+        <v>0.236487</v>
+      </c>
       <c r="AI10" s="13">
         <f>IF(OR(AG10="",AH10=""),"",AH10-AG10)</f>
         <v/>
       </c>
-      <c r="AJ10" s="12" t="n"/>
-      <c r="AK10" s="12" t="n"/>
+      <c r="AJ10" s="12" t="n">
+        <v>0.046718</v>
+      </c>
+      <c r="AK10" s="12" t="n">
+        <v>0.051265</v>
+      </c>
       <c r="AL10" s="13">
         <f>IF(OR(AJ10="",AK10=""),"",AK10-AJ10)</f>
         <v/>
       </c>
-      <c r="AM10" s="10" t="n"/>
-      <c r="AN10" s="10" t="n"/>
+      <c r="AM10" s="10" t="n">
+        <v>4368</v>
+      </c>
+      <c r="AN10" s="10" t="n">
+        <v>4368</v>
+      </c>
       <c r="AO10" s="11">
         <f>IF(OR(AM10="",AN10=""),"",AN10-AM10)</f>
         <v/>
       </c>
-      <c r="AP10" s="10" t="n"/>
-      <c r="AQ10" s="10" t="n"/>
+      <c r="AP10" s="10" t="n">
+        <v>16.898626</v>
+      </c>
+      <c r="AQ10" s="10" t="n">
+        <v>11.267651</v>
+      </c>
       <c r="AR10" s="11">
         <f>IF(OR(AP10="",AQ10=""),"",AQ10-AP10)</f>
         <v/>
       </c>
-      <c r="AS10" s="10" t="n"/>
-      <c r="AT10" s="10" t="n"/>
+      <c r="AS10" s="10" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="AT10" s="10" t="n">
+        <v>26.7</v>
+      </c>
       <c r="AU10" s="11">
         <f>IF(OR(AS10="",AT10=""),"",AT10-AS10)</f>
         <v/>
@@ -2252,92 +2432,152 @@
       <c r="B11" s="9" t="n">
         <v>20260926</v>
       </c>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="n"/>
+      <c r="C11" s="10" t="n">
+        <v>18384</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>18384</v>
+      </c>
       <c r="E11" s="11">
         <f>IF(OR(C11="",D11=""),"",D11-C11)</f>
         <v/>
       </c>
-      <c r="F11" s="10" t="n"/>
-      <c r="G11" s="10" t="n"/>
+      <c r="F11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H11" s="11">
         <f>IF(OR(F11="",G11=""),"",G11-F11)</f>
         <v/>
       </c>
-      <c r="I11" s="10" t="n"/>
-      <c r="J11" s="10" t="n"/>
+      <c r="I11" s="10" t="n">
+        <v>18174</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>18176</v>
+      </c>
       <c r="K11" s="11">
         <f>IF(OR(I11="",J11=""),"",J11-I11)</f>
         <v/>
       </c>
-      <c r="L11" s="10" t="n"/>
-      <c r="M11" s="10" t="n"/>
+      <c r="L11" s="10" t="n">
+        <v>18384</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>18384</v>
+      </c>
       <c r="N11" s="11">
         <f>IF(OR(L11="",M11=""),"",M11-L11)</f>
         <v/>
       </c>
-      <c r="O11" s="10" t="n"/>
-      <c r="P11" s="10" t="n"/>
+      <c r="O11" s="10" t="n">
+        <v>10.707376</v>
+      </c>
+      <c r="P11" s="10" t="n">
+        <v>7.470561</v>
+      </c>
       <c r="Q11" s="11">
         <f>IF(OR(O11="",P11=""),"",P11-O11)</f>
         <v/>
       </c>
-      <c r="R11" s="10" t="n"/>
-      <c r="S11" s="10" t="n"/>
+      <c r="R11" s="10" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="S11" s="10" t="n">
+        <v>18.9</v>
+      </c>
       <c r="T11" s="11">
         <f>IF(OR(R11="",S11=""),"",S11-R11)</f>
         <v/>
       </c>
-      <c r="U11" s="12" t="n"/>
-      <c r="V11" s="12" t="n"/>
+      <c r="U11" s="12" t="n">
+        <v>0.083388</v>
+      </c>
+      <c r="V11" s="12" t="n">
+        <v>0.02203</v>
+      </c>
       <c r="W11" s="13">
         <f>IF(OR(U11="",V11=""),"",V11-U11)</f>
         <v/>
       </c>
-      <c r="X11" s="10" t="n"/>
-      <c r="Y11" s="10" t="n"/>
+      <c r="X11" s="10" t="n">
+        <v>21.815367</v>
+      </c>
+      <c r="Y11" s="10" t="n">
+        <v>15.211367</v>
+      </c>
       <c r="Z11" s="11">
         <f>IF(OR(X11="",Y11=""),"",Y11-X11)</f>
         <v/>
       </c>
-      <c r="AA11" s="10" t="n"/>
-      <c r="AB11" s="10" t="n"/>
+      <c r="AA11" s="10" t="n">
+        <v>229</v>
+      </c>
+      <c r="AB11" s="10" t="n">
+        <v>167</v>
+      </c>
       <c r="AC11" s="11">
         <f>IF(OR(AA11="",AB11=""),"",AB11-AA11)</f>
         <v/>
       </c>
-      <c r="AD11" s="10" t="n"/>
-      <c r="AE11" s="10" t="n"/>
+      <c r="AD11" s="10" t="n">
+        <v>61.280786</v>
+      </c>
+      <c r="AE11" s="10" t="n">
+        <v>62.180786</v>
+      </c>
       <c r="AF11" s="11">
         <f>IF(OR(AD11="",AE11=""),"",AE11-AD11)</f>
         <v/>
       </c>
-      <c r="AG11" s="12" t="n"/>
-      <c r="AH11" s="12" t="n"/>
+      <c r="AG11" s="12" t="n">
+        <v>0.260777</v>
+      </c>
+      <c r="AH11" s="12" t="n">
+        <v>0.237082</v>
+      </c>
       <c r="AI11" s="13">
         <f>IF(OR(AG11="",AH11=""),"",AH11-AG11)</f>
         <v/>
       </c>
-      <c r="AJ11" s="12" t="n"/>
-      <c r="AK11" s="12" t="n"/>
+      <c r="AJ11" s="12" t="n">
+        <v>0.04796</v>
+      </c>
+      <c r="AK11" s="12" t="n">
+        <v>0.051282</v>
+      </c>
       <c r="AL11" s="13">
         <f>IF(OR(AJ11="",AK11=""),"",AK11-AJ11)</f>
         <v/>
       </c>
-      <c r="AM11" s="10" t="n"/>
-      <c r="AN11" s="10" t="n"/>
+      <c r="AM11" s="10" t="n">
+        <v>4389</v>
+      </c>
+      <c r="AN11" s="10" t="n">
+        <v>4389</v>
+      </c>
       <c r="AO11" s="11">
         <f>IF(OR(AM11="",AN11=""),"",AN11-AM11)</f>
         <v/>
       </c>
-      <c r="AP11" s="10" t="n"/>
-      <c r="AQ11" s="10" t="n"/>
+      <c r="AP11" s="10" t="n">
+        <v>16.62406</v>
+      </c>
+      <c r="AQ11" s="10" t="n">
+        <v>11.211483</v>
+      </c>
       <c r="AR11" s="11">
         <f>IF(OR(AP11="",AQ11=""),"",AQ11-AP11)</f>
         <v/>
       </c>
-      <c r="AS11" s="10" t="n"/>
-      <c r="AT11" s="10" t="n"/>
+      <c r="AS11" s="10" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="AT11" s="10" t="n">
+        <v>26.4</v>
+      </c>
       <c r="AU11" s="11">
         <f>IF(OR(AS11="",AT11=""),"",AT11-AS11)</f>
         <v/>
@@ -2350,92 +2590,152 @@
       <c r="B12" s="9" t="n">
         <v>20260927</v>
       </c>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
+      <c r="C12" s="10" t="n">
+        <v>18542</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>18542</v>
+      </c>
       <c r="E12" s="11">
         <f>IF(OR(C12="",D12=""),"",D12-C12)</f>
         <v/>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H12" s="11">
         <f>IF(OR(F12="",G12=""),"",G12-F12)</f>
         <v/>
       </c>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
+      <c r="I12" s="10" t="n">
+        <v>18329</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>18331</v>
+      </c>
       <c r="K12" s="11">
         <f>IF(OR(I12="",J12=""),"",J12-I12)</f>
         <v/>
       </c>
-      <c r="L12" s="10" t="n"/>
-      <c r="M12" s="10" t="n"/>
+      <c r="L12" s="10" t="n">
+        <v>18542</v>
+      </c>
+      <c r="M12" s="10" t="n">
+        <v>18542</v>
+      </c>
       <c r="N12" s="11">
         <f>IF(OR(L12="",M12=""),"",M12-L12)</f>
         <v/>
       </c>
-      <c r="O12" s="10" t="n"/>
-      <c r="P12" s="10" t="n"/>
+      <c r="O12" s="10" t="n">
+        <v>10.925698</v>
+      </c>
+      <c r="P12" s="10" t="n">
+        <v>7.478821</v>
+      </c>
       <c r="Q12" s="11">
         <f>IF(OR(O12="",P12=""),"",P12-O12)</f>
         <v/>
       </c>
-      <c r="R12" s="10" t="n"/>
-      <c r="S12" s="10" t="n"/>
+      <c r="R12" s="10" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="S12" s="10" t="n">
+        <v>18.9</v>
+      </c>
       <c r="T12" s="11">
         <f>IF(OR(R12="",S12=""),"",S12-R12)</f>
         <v/>
       </c>
-      <c r="U12" s="12" t="n"/>
-      <c r="V12" s="12" t="n"/>
+      <c r="U12" s="12" t="n">
+        <v>0.089742</v>
+      </c>
+      <c r="V12" s="12" t="n">
+        <v>0.021519</v>
+      </c>
       <c r="W12" s="13">
         <f>IF(OR(U12="",V12=""),"",V12-U12)</f>
         <v/>
       </c>
-      <c r="X12" s="10" t="n"/>
-      <c r="Y12" s="10" t="n"/>
+      <c r="X12" s="10" t="n">
+        <v>22.4425</v>
+      </c>
+      <c r="Y12" s="10" t="n">
+        <v>15.359067</v>
+      </c>
       <c r="Z12" s="11">
         <f>IF(OR(X12="",Y12=""),"",Y12-X12)</f>
         <v/>
       </c>
-      <c r="AA12" s="10" t="n"/>
-      <c r="AB12" s="10" t="n"/>
+      <c r="AA12" s="10" t="n">
+        <v>222</v>
+      </c>
+      <c r="AB12" s="10" t="n">
+        <v>162</v>
+      </c>
       <c r="AC12" s="11">
         <f>IF(OR(AA12="",AB12=""),"",AB12-AA12)</f>
         <v/>
       </c>
-      <c r="AD12" s="10" t="n"/>
-      <c r="AE12" s="10" t="n"/>
+      <c r="AD12" s="10" t="n">
+        <v>66.680786</v>
+      </c>
+      <c r="AE12" s="10" t="n">
+        <v>64.880786</v>
+      </c>
       <c r="AF12" s="11">
         <f>IF(OR(AD12="",AE12=""),"",AE12-AD12)</f>
         <v/>
       </c>
-      <c r="AG12" s="12" t="n"/>
-      <c r="AH12" s="12" t="n"/>
+      <c r="AG12" s="12" t="n">
+        <v>0.26247</v>
+      </c>
+      <c r="AH12" s="12" t="n">
+        <v>0.238701</v>
+      </c>
       <c r="AI12" s="13">
         <f>IF(OR(AG12="",AH12=""),"",AH12-AG12)</f>
         <v/>
       </c>
-      <c r="AJ12" s="12" t="n"/>
-      <c r="AK12" s="12" t="n"/>
+      <c r="AJ12" s="12" t="n">
+        <v>0.049203</v>
+      </c>
+      <c r="AK12" s="12" t="n">
+        <v>0.052234</v>
+      </c>
       <c r="AL12" s="13">
         <f>IF(OR(AJ12="",AK12=""),"",AK12-AJ12)</f>
         <v/>
       </c>
-      <c r="AM12" s="10" t="n"/>
-      <c r="AN12" s="10" t="n"/>
+      <c r="AM12" s="10" t="n">
+        <v>4393</v>
+      </c>
+      <c r="AN12" s="10" t="n">
+        <v>4393</v>
+      </c>
       <c r="AO12" s="11">
         <f>IF(OR(AM12="",AN12=""),"",AN12-AM12)</f>
         <v/>
       </c>
-      <c r="AP12" s="10" t="n"/>
-      <c r="AQ12" s="10" t="n"/>
+      <c r="AP12" s="10" t="n">
+        <v>16.093945</v>
+      </c>
+      <c r="AQ12" s="10" t="n">
+        <v>10.786342</v>
+      </c>
       <c r="AR12" s="11">
         <f>IF(OR(AP12="",AQ12=""),"",AQ12-AP12)</f>
         <v/>
       </c>
-      <c r="AS12" s="10" t="n"/>
-      <c r="AT12" s="10" t="n"/>
+      <c r="AS12" s="10" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="AT12" s="10" t="n">
+        <v>25.8</v>
+      </c>
       <c r="AU12" s="11">
         <f>IF(OR(AS12="",AT12=""),"",AT12-AS12)</f>
         <v/>
@@ -2448,92 +2748,152 @@
       <c r="B13" s="9" t="n">
         <v>20260928</v>
       </c>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
+      <c r="C13" s="10" t="n">
+        <v>18358</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>18358</v>
+      </c>
       <c r="E13" s="11">
         <f>IF(OR(C13="",D13=""),"",D13-C13)</f>
         <v/>
       </c>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
+      <c r="F13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H13" s="11">
         <f>IF(OR(F13="",G13=""),"",G13-F13)</f>
         <v/>
       </c>
-      <c r="I13" s="10" t="n"/>
-      <c r="J13" s="10" t="n"/>
+      <c r="I13" s="10" t="n">
+        <v>18143</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>18139</v>
+      </c>
       <c r="K13" s="11">
         <f>IF(OR(I13="",J13=""),"",J13-I13)</f>
         <v/>
       </c>
-      <c r="L13" s="10" t="n"/>
-      <c r="M13" s="10" t="n"/>
+      <c r="L13" s="10" t="n">
+        <v>18358</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>18358</v>
+      </c>
       <c r="N13" s="11">
         <f>IF(OR(L13="",M13=""),"",M13-L13)</f>
         <v/>
       </c>
-      <c r="O13" s="10" t="n"/>
-      <c r="P13" s="10" t="n"/>
+      <c r="O13" s="10" t="n">
+        <v>11.072579</v>
+      </c>
+      <c r="P13" s="10" t="n">
+        <v>7.532177</v>
+      </c>
       <c r="Q13" s="11">
         <f>IF(OR(O13="",P13=""),"",P13-O13)</f>
         <v/>
       </c>
-      <c r="R13" s="10" t="n"/>
-      <c r="S13" s="10" t="n"/>
+      <c r="R13" s="10" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="S13" s="10" t="n">
+        <v>18.9</v>
+      </c>
       <c r="T13" s="11">
         <f>IF(OR(R13="",S13=""),"",S13-R13)</f>
         <v/>
       </c>
-      <c r="U13" s="12" t="n"/>
-      <c r="V13" s="12" t="n"/>
+      <c r="U13" s="12" t="n">
+        <v>0.08955200000000001</v>
+      </c>
+      <c r="V13" s="12" t="n">
+        <v>0.025711</v>
+      </c>
       <c r="W13" s="13">
         <f>IF(OR(U13="",V13=""),"",V13-U13)</f>
         <v/>
       </c>
-      <c r="X13" s="10" t="n"/>
-      <c r="Y13" s="10" t="n"/>
+      <c r="X13" s="10" t="n">
+        <v>22.522033</v>
+      </c>
+      <c r="Y13" s="10" t="n">
+        <v>15.310633</v>
+      </c>
       <c r="Z13" s="11">
         <f>IF(OR(X13="",Y13=""),"",Y13-X13)</f>
         <v/>
       </c>
-      <c r="AA13" s="10" t="n"/>
-      <c r="AB13" s="10" t="n"/>
+      <c r="AA13" s="10" t="n">
+        <v>234</v>
+      </c>
+      <c r="AB13" s="10" t="n">
+        <v>175</v>
+      </c>
       <c r="AC13" s="11">
         <f>IF(OR(AA13="",AB13=""),"",AB13-AA13)</f>
         <v/>
       </c>
-      <c r="AD13" s="10" t="n"/>
-      <c r="AE13" s="10" t="n"/>
+      <c r="AD13" s="10" t="n">
+        <v>63.380786</v>
+      </c>
+      <c r="AE13" s="10" t="n">
+        <v>63.980786</v>
+      </c>
       <c r="AF13" s="11">
         <f>IF(OR(AD13="",AE13=""),"",AE13-AD13)</f>
         <v/>
       </c>
-      <c r="AG13" s="12" t="n"/>
-      <c r="AH13" s="12" t="n"/>
+      <c r="AG13" s="12" t="n">
+        <v>0.259646</v>
+      </c>
+      <c r="AH13" s="12" t="n">
+        <v>0.236055</v>
+      </c>
       <c r="AI13" s="13">
         <f>IF(OR(AG13="",AH13=""),"",AH13-AG13)</f>
         <v/>
       </c>
-      <c r="AJ13" s="12" t="n"/>
-      <c r="AK13" s="12" t="n"/>
+      <c r="AJ13" s="12" t="n">
+        <v>0.046245</v>
+      </c>
+      <c r="AK13" s="12" t="n">
+        <v>0.04984</v>
+      </c>
       <c r="AL13" s="13">
         <f>IF(OR(AJ13="",AK13=""),"",AK13-AJ13)</f>
         <v/>
       </c>
-      <c r="AM13" s="10" t="n"/>
-      <c r="AN13" s="10" t="n"/>
+      <c r="AM13" s="10" t="n">
+        <v>4392</v>
+      </c>
+      <c r="AN13" s="10" t="n">
+        <v>4392</v>
+      </c>
       <c r="AO13" s="11">
         <f>IF(OR(AM13="",AN13=""),"",AN13-AM13)</f>
         <v/>
       </c>
-      <c r="AP13" s="10" t="n"/>
-      <c r="AQ13" s="10" t="n"/>
+      <c r="AP13" s="10" t="n">
+        <v>16.783675</v>
+      </c>
+      <c r="AQ13" s="10" t="n">
+        <v>11.305191</v>
+      </c>
       <c r="AR13" s="11">
         <f>IF(OR(AP13="",AQ13=""),"",AQ13-AP13)</f>
         <v/>
       </c>
-      <c r="AS13" s="10" t="n"/>
-      <c r="AT13" s="10" t="n"/>
+      <c r="AS13" s="10" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="AT13" s="10" t="n">
+        <v>27.9</v>
+      </c>
       <c r="AU13" s="11">
         <f>IF(OR(AS13="",AT13=""),"",AT13-AS13)</f>
         <v/>
@@ -2546,92 +2906,152 @@
       <c r="B14" s="9" t="n">
         <v>20260929</v>
       </c>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
+      <c r="C14" s="10" t="n">
+        <v>18432</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>18432</v>
+      </c>
       <c r="E14" s="11">
         <f>IF(OR(C14="",D14=""),"",D14-C14)</f>
         <v/>
       </c>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
+      <c r="F14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H14" s="11">
         <f>IF(OR(F14="",G14=""),"",G14-F14)</f>
         <v/>
       </c>
-      <c r="I14" s="10" t="n"/>
-      <c r="J14" s="10" t="n"/>
+      <c r="I14" s="10" t="n">
+        <v>18219</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>18220</v>
+      </c>
       <c r="K14" s="11">
         <f>IF(OR(I14="",J14=""),"",J14-I14)</f>
         <v/>
       </c>
-      <c r="L14" s="10" t="n"/>
-      <c r="M14" s="10" t="n"/>
+      <c r="L14" s="10" t="n">
+        <v>18432</v>
+      </c>
+      <c r="M14" s="10" t="n">
+        <v>18432</v>
+      </c>
       <c r="N14" s="11">
         <f>IF(OR(L14="",M14=""),"",M14-L14)</f>
         <v/>
       </c>
-      <c r="O14" s="10" t="n"/>
-      <c r="P14" s="10" t="n"/>
+      <c r="O14" s="10" t="n">
+        <v>10.920817</v>
+      </c>
+      <c r="P14" s="10" t="n">
+        <v>7.389209</v>
+      </c>
       <c r="Q14" s="11">
         <f>IF(OR(O14="",P14=""),"",P14-O14)</f>
         <v/>
       </c>
-      <c r="R14" s="10" t="n"/>
-      <c r="S14" s="10" t="n"/>
+      <c r="R14" s="10" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="S14" s="10" t="n">
+        <v>18.6</v>
+      </c>
       <c r="T14" s="11">
         <f>IF(OR(R14="",S14=""),"",S14-R14)</f>
         <v/>
       </c>
-      <c r="U14" s="12" t="n"/>
-      <c r="V14" s="12" t="n"/>
+      <c r="U14" s="12" t="n">
+        <v>0.086968</v>
+      </c>
+      <c r="V14" s="12" t="n">
+        <v>0.021213</v>
+      </c>
       <c r="W14" s="13">
         <f>IF(OR(U14="",V14=""),"",V14-U14)</f>
         <v/>
       </c>
-      <c r="X14" s="10" t="n"/>
-      <c r="Y14" s="10" t="n"/>
+      <c r="X14" s="10" t="n">
+        <v>22.304633</v>
+      </c>
+      <c r="Y14" s="10" t="n">
+        <v>15.070933</v>
+      </c>
       <c r="Z14" s="11">
         <f>IF(OR(X14="",Y14=""),"",Y14-X14)</f>
         <v/>
       </c>
-      <c r="AA14" s="10" t="n"/>
-      <c r="AB14" s="10" t="n"/>
+      <c r="AA14" s="10" t="n">
+        <v>227</v>
+      </c>
+      <c r="AB14" s="10" t="n">
+        <v>165</v>
+      </c>
       <c r="AC14" s="11">
         <f>IF(OR(AA14="",AB14=""),"",AB14-AA14)</f>
         <v/>
       </c>
-      <c r="AD14" s="10" t="n"/>
-      <c r="AE14" s="10" t="n"/>
+      <c r="AD14" s="10" t="n">
+        <v>64.28078600000001</v>
+      </c>
+      <c r="AE14" s="10" t="n">
+        <v>67.580786</v>
+      </c>
       <c r="AF14" s="11">
         <f>IF(OR(AD14="",AE14=""),"",AE14-AD14)</f>
         <v/>
       </c>
-      <c r="AG14" s="12" t="n"/>
-      <c r="AH14" s="12" t="n"/>
+      <c r="AG14" s="12" t="n">
+        <v>0.260909</v>
+      </c>
+      <c r="AH14" s="12" t="n">
+        <v>0.237153</v>
+      </c>
       <c r="AI14" s="13">
         <f>IF(OR(AG14="",AH14=""),"",AH14-AG14)</f>
         <v/>
       </c>
-      <c r="AJ14" s="12" t="n"/>
-      <c r="AK14" s="12" t="n"/>
+      <c r="AJ14" s="12" t="n">
+        <v>0.047948</v>
+      </c>
+      <c r="AK14" s="12" t="n">
+        <v>0.051175</v>
+      </c>
       <c r="AL14" s="13">
         <f>IF(OR(AJ14="",AK14=""),"",AK14-AJ14)</f>
         <v/>
       </c>
-      <c r="AM14" s="10" t="n"/>
-      <c r="AN14" s="10" t="n"/>
+      <c r="AM14" s="10" t="n">
+        <v>4358</v>
+      </c>
+      <c r="AN14" s="10" t="n">
+        <v>4358</v>
+      </c>
       <c r="AO14" s="11">
         <f>IF(OR(AM14="",AN14=""),"",AN14-AM14)</f>
         <v/>
       </c>
-      <c r="AP14" s="10" t="n"/>
-      <c r="AQ14" s="10" t="n"/>
+      <c r="AP14" s="10" t="n">
+        <v>15.816292</v>
+      </c>
+      <c r="AQ14" s="10" t="n">
+        <v>10.584878</v>
+      </c>
       <c r="AR14" s="11">
         <f>IF(OR(AP14="",AQ14=""),"",AQ14-AP14)</f>
         <v/>
       </c>
-      <c r="AS14" s="10" t="n"/>
-      <c r="AT14" s="10" t="n"/>
+      <c r="AS14" s="10" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="AT14" s="10" t="n">
+        <v>25.5</v>
+      </c>
       <c r="AU14" s="11">
         <f>IF(OR(AS14="",AT14=""),"",AT14-AS14)</f>
         <v/>
@@ -2644,92 +3064,152 @@
       <c r="B15" s="9" t="n">
         <v>20260930</v>
       </c>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
+      <c r="C15" s="10" t="n">
+        <v>18404</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>18404</v>
+      </c>
       <c r="E15" s="11">
         <f>IF(OR(C15="",D15=""),"",D15-C15)</f>
         <v/>
       </c>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="10" t="n"/>
+      <c r="F15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H15" s="11">
         <f>IF(OR(F15="",G15=""),"",G15-F15)</f>
         <v/>
       </c>
-      <c r="I15" s="10" t="n"/>
-      <c r="J15" s="10" t="n"/>
+      <c r="I15" s="10" t="n">
+        <v>18205</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>18202</v>
+      </c>
       <c r="K15" s="11">
         <f>IF(OR(I15="",J15=""),"",J15-I15)</f>
         <v/>
       </c>
-      <c r="L15" s="10" t="n"/>
-      <c r="M15" s="10" t="n"/>
+      <c r="L15" s="10" t="n">
+        <v>18404</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>18404</v>
+      </c>
       <c r="N15" s="11">
         <f>IF(OR(L15="",M15=""),"",M15-L15)</f>
         <v/>
       </c>
-      <c r="O15" s="10" t="n"/>
-      <c r="P15" s="10" t="n"/>
+      <c r="O15" s="10" t="n">
+        <v>11.210291</v>
+      </c>
+      <c r="P15" s="10" t="n">
+        <v>7.678429</v>
+      </c>
       <c r="Q15" s="11">
         <f>IF(OR(O15="",P15=""),"",P15-O15)</f>
         <v/>
       </c>
-      <c r="R15" s="10" t="n"/>
-      <c r="S15" s="10" t="n"/>
+      <c r="R15" s="10" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="S15" s="10" t="n">
+        <v>19.5</v>
+      </c>
       <c r="T15" s="11">
         <f>IF(OR(R15="",S15=""),"",S15-R15)</f>
         <v/>
       </c>
-      <c r="U15" s="12" t="n"/>
-      <c r="V15" s="12" t="n"/>
+      <c r="U15" s="12" t="n">
+        <v>0.09503399999999999</v>
+      </c>
+      <c r="V15" s="12" t="n">
+        <v>0.02945</v>
+      </c>
       <c r="W15" s="13">
         <f>IF(OR(U15="",V15=""),"",V15-U15)</f>
         <v/>
       </c>
-      <c r="X15" s="10" t="n"/>
-      <c r="Y15" s="10" t="n"/>
+      <c r="X15" s="10" t="n">
+        <v>22.858833</v>
+      </c>
+      <c r="Y15" s="10" t="n">
+        <v>15.6505</v>
+      </c>
       <c r="Z15" s="11">
         <f>IF(OR(X15="",Y15=""),"",Y15-X15)</f>
         <v/>
       </c>
-      <c r="AA15" s="10" t="n"/>
-      <c r="AB15" s="10" t="n"/>
+      <c r="AA15" s="10" t="n">
+        <v>236</v>
+      </c>
+      <c r="AB15" s="10" t="n">
+        <v>174</v>
+      </c>
       <c r="AC15" s="11">
         <f>IF(OR(AA15="",AB15=""),"",AB15-AA15)</f>
         <v/>
       </c>
-      <c r="AD15" s="10" t="n"/>
-      <c r="AE15" s="10" t="n"/>
+      <c r="AD15" s="10" t="n">
+        <v>69.680786</v>
+      </c>
+      <c r="AE15" s="10" t="n">
+        <v>62.780786</v>
+      </c>
       <c r="AF15" s="11">
         <f>IF(OR(AD15="",AE15=""),"",AE15-AD15)</f>
         <v/>
       </c>
-      <c r="AG15" s="12" t="n"/>
-      <c r="AH15" s="12" t="n"/>
+      <c r="AG15" s="12" t="n">
+        <v>0.260334</v>
+      </c>
+      <c r="AH15" s="12" t="n">
+        <v>0.236732</v>
+      </c>
       <c r="AI15" s="13">
         <f>IF(OR(AG15="",AH15=""),"",AH15-AG15)</f>
         <v/>
       </c>
-      <c r="AJ15" s="12" t="n"/>
-      <c r="AK15" s="12" t="n"/>
+      <c r="AJ15" s="12" t="n">
+        <v>0.046776</v>
+      </c>
+      <c r="AK15" s="12" t="n">
+        <v>0.051596</v>
+      </c>
       <c r="AL15" s="13">
         <f>IF(OR(AJ15="",AK15=""),"",AK15-AJ15)</f>
         <v/>
       </c>
-      <c r="AM15" s="10" t="n"/>
-      <c r="AN15" s="10" t="n"/>
+      <c r="AM15" s="10" t="n">
+        <v>4399</v>
+      </c>
+      <c r="AN15" s="10" t="n">
+        <v>4399</v>
+      </c>
       <c r="AO15" s="11">
         <f>IF(OR(AM15="",AN15=""),"",AN15-AM15)</f>
         <v/>
       </c>
-      <c r="AP15" s="10" t="n"/>
-      <c r="AQ15" s="10" t="n"/>
+      <c r="AP15" s="10" t="n">
+        <v>16.656172</v>
+      </c>
+      <c r="AQ15" s="10" t="n">
+        <v>11.048579</v>
+      </c>
       <c r="AR15" s="11">
         <f>IF(OR(AP15="",AQ15=""),"",AQ15-AP15)</f>
         <v/>
       </c>
-      <c r="AS15" s="10" t="n"/>
-      <c r="AT15" s="10" t="n"/>
+      <c r="AS15" s="10" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="AT15" s="10" t="n">
+        <v>26.7</v>
+      </c>
       <c r="AU15" s="11">
         <f>IF(OR(AS15="",AT15=""),"",AT15-AS15)</f>
         <v/>
@@ -2742,92 +3222,152 @@
       <c r="B16" s="9" t="n">
         <v>20260931</v>
       </c>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="10" t="n"/>
+      <c r="C16" s="10" t="n">
+        <v>18491</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>18491</v>
+      </c>
       <c r="E16" s="11">
         <f>IF(OR(C16="",D16=""),"",D16-C16)</f>
         <v/>
       </c>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
+      <c r="F16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H16" s="11">
         <f>IF(OR(F16="",G16=""),"",G16-F16)</f>
         <v/>
       </c>
-      <c r="I16" s="10" t="n"/>
-      <c r="J16" s="10" t="n"/>
+      <c r="I16" s="10" t="n">
+        <v>18287</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>18289</v>
+      </c>
       <c r="K16" s="11">
         <f>IF(OR(I16="",J16=""),"",J16-I16)</f>
         <v/>
       </c>
-      <c r="L16" s="10" t="n"/>
-      <c r="M16" s="10" t="n"/>
+      <c r="L16" s="10" t="n">
+        <v>18491</v>
+      </c>
+      <c r="M16" s="10" t="n">
+        <v>18491</v>
+      </c>
       <c r="N16" s="11">
         <f>IF(OR(L16="",M16=""),"",M16-L16)</f>
         <v/>
       </c>
-      <c r="O16" s="10" t="n"/>
-      <c r="P16" s="10" t="n"/>
+      <c r="O16" s="10" t="n">
+        <v>10.987275</v>
+      </c>
+      <c r="P16" s="10" t="n">
+        <v>7.569699</v>
+      </c>
       <c r="Q16" s="11">
         <f>IF(OR(O16="",P16=""),"",P16-O16)</f>
         <v/>
       </c>
-      <c r="R16" s="10" t="n"/>
-      <c r="S16" s="10" t="n"/>
+      <c r="R16" s="10" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="S16" s="10" t="n">
+        <v>18.9</v>
+      </c>
       <c r="T16" s="11">
         <f>IF(OR(R16="",S16=""),"",S16-R16)</f>
         <v/>
       </c>
-      <c r="U16" s="12" t="n"/>
-      <c r="V16" s="12" t="n"/>
+      <c r="U16" s="12" t="n">
+        <v>0.086204</v>
+      </c>
+      <c r="V16" s="12" t="n">
+        <v>0.022714</v>
+      </c>
       <c r="W16" s="13">
         <f>IF(OR(U16="",V16=""),"",V16-U16)</f>
         <v/>
       </c>
-      <c r="X16" s="10" t="n"/>
-      <c r="Y16" s="10" t="n"/>
+      <c r="X16" s="10" t="n">
+        <v>22.515933</v>
+      </c>
+      <c r="Y16" s="10" t="n">
+        <v>15.503333</v>
+      </c>
       <c r="Z16" s="11">
         <f>IF(OR(X16="",Y16=""),"",Y16-X16)</f>
         <v/>
       </c>
-      <c r="AA16" s="10" t="n"/>
-      <c r="AB16" s="10" t="n"/>
+      <c r="AA16" s="10" t="n">
+        <v>243</v>
+      </c>
+      <c r="AB16" s="10" t="n">
+        <v>184</v>
+      </c>
       <c r="AC16" s="11">
         <f>IF(OR(AA16="",AB16=""),"",AB16-AA16)</f>
         <v/>
       </c>
-      <c r="AD16" s="10" t="n"/>
-      <c r="AE16" s="10" t="n"/>
+      <c r="AD16" s="10" t="n">
+        <v>63.980786</v>
+      </c>
+      <c r="AE16" s="10" t="n">
+        <v>61.280786</v>
+      </c>
       <c r="AF16" s="11">
         <f>IF(OR(AD16="",AE16=""),"",AE16-AD16)</f>
         <v/>
       </c>
-      <c r="AG16" s="12" t="n"/>
-      <c r="AH16" s="12" t="n"/>
+      <c r="AG16" s="12" t="n">
+        <v>0.261692</v>
+      </c>
+      <c r="AH16" s="12" t="n">
+        <v>0.237926</v>
+      </c>
       <c r="AI16" s="13">
         <f>IF(OR(AG16="",AH16=""),"",AH16-AG16)</f>
         <v/>
       </c>
-      <c r="AJ16" s="12" t="n"/>
-      <c r="AK16" s="12" t="n"/>
+      <c r="AJ16" s="12" t="n">
+        <v>0.047376</v>
+      </c>
+      <c r="AK16" s="12" t="n">
+        <v>0.051549</v>
+      </c>
       <c r="AL16" s="13">
         <f>IF(OR(AJ16="",AK16=""),"",AK16-AJ16)</f>
         <v/>
       </c>
-      <c r="AM16" s="10" t="n"/>
-      <c r="AN16" s="10" t="n"/>
+      <c r="AM16" s="10" t="n">
+        <v>4384</v>
+      </c>
+      <c r="AN16" s="10" t="n">
+        <v>4384</v>
+      </c>
       <c r="AO16" s="11">
         <f>IF(OR(AM16="",AN16=""),"",AN16-AM16)</f>
         <v/>
       </c>
-      <c r="AP16" s="10" t="n"/>
-      <c r="AQ16" s="10" t="n"/>
+      <c r="AP16" s="10" t="n">
+        <v>16.500068</v>
+      </c>
+      <c r="AQ16" s="10" t="n">
+        <v>11.476711</v>
+      </c>
       <c r="AR16" s="11">
         <f>IF(OR(AP16="",AQ16=""),"",AQ16-AP16)</f>
         <v/>
       </c>
-      <c r="AS16" s="10" t="n"/>
-      <c r="AT16" s="10" t="n"/>
+      <c r="AS16" s="10" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="AT16" s="10" t="n">
+        <v>27.3</v>
+      </c>
       <c r="AU16" s="11">
         <f>IF(OR(AS16="",AT16=""),"",AT16-AS16)</f>
         <v/>
@@ -2840,92 +3380,152 @@
       <c r="B17" s="9" t="n">
         <v>20260932</v>
       </c>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
+      <c r="C17" s="10" t="n">
+        <v>18358</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>18358</v>
+      </c>
       <c r="E17" s="11">
         <f>IF(OR(C17="",D17=""),"",D17-C17)</f>
         <v/>
       </c>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="10" t="n"/>
+      <c r="F17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H17" s="11">
         <f>IF(OR(F17="",G17=""),"",G17-F17)</f>
         <v/>
       </c>
-      <c r="I17" s="10" t="n"/>
-      <c r="J17" s="10" t="n"/>
+      <c r="I17" s="10" t="n">
+        <v>18152</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>18152</v>
+      </c>
       <c r="K17" s="11">
         <f>IF(OR(I17="",J17=""),"",J17-I17)</f>
         <v/>
       </c>
-      <c r="L17" s="10" t="n"/>
-      <c r="M17" s="10" t="n"/>
+      <c r="L17" s="10" t="n">
+        <v>18358</v>
+      </c>
+      <c r="M17" s="10" t="n">
+        <v>18358</v>
+      </c>
       <c r="N17" s="11">
         <f>IF(OR(L17="",M17=""),"",M17-L17)</f>
         <v/>
       </c>
-      <c r="O17" s="10" t="n"/>
-      <c r="P17" s="10" t="n"/>
+      <c r="O17" s="10" t="n">
+        <v>10.741105</v>
+      </c>
+      <c r="P17" s="10" t="n">
+        <v>7.385625</v>
+      </c>
       <c r="Q17" s="11">
         <f>IF(OR(O17="",P17=""),"",P17-O17)</f>
         <v/>
       </c>
-      <c r="R17" s="10" t="n"/>
-      <c r="S17" s="10" t="n"/>
+      <c r="R17" s="10" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="S17" s="10" t="n">
+        <v>18.6</v>
+      </c>
       <c r="T17" s="11">
         <f>IF(OR(R17="",S17=""),"",S17-R17)</f>
         <v/>
       </c>
-      <c r="U17" s="12" t="n"/>
-      <c r="V17" s="12" t="n"/>
+      <c r="U17" s="12" t="n">
+        <v>0.08214399999999999</v>
+      </c>
+      <c r="V17" s="12" t="n">
+        <v>0.020808</v>
+      </c>
       <c r="W17" s="13">
         <f>IF(OR(U17="",V17=""),"",V17-U17)</f>
         <v/>
       </c>
-      <c r="X17" s="10" t="n"/>
-      <c r="Y17" s="10" t="n"/>
+      <c r="X17" s="10" t="n">
+        <v>21.855933</v>
+      </c>
+      <c r="Y17" s="10" t="n">
+        <v>15.021833</v>
+      </c>
       <c r="Z17" s="11">
         <f>IF(OR(X17="",Y17=""),"",Y17-X17)</f>
         <v/>
       </c>
-      <c r="AA17" s="10" t="n"/>
-      <c r="AB17" s="10" t="n"/>
+      <c r="AA17" s="10" t="n">
+        <v>227</v>
+      </c>
+      <c r="AB17" s="10" t="n">
+        <v>171</v>
+      </c>
       <c r="AC17" s="11">
         <f>IF(OR(AA17="",AB17=""),"",AB17-AA17)</f>
         <v/>
       </c>
-      <c r="AD17" s="10" t="n"/>
-      <c r="AE17" s="10" t="n"/>
+      <c r="AD17" s="10" t="n">
+        <v>64.580786</v>
+      </c>
+      <c r="AE17" s="10" t="n">
+        <v>65.180786</v>
+      </c>
       <c r="AF17" s="11">
         <f>IF(OR(AD17="",AE17=""),"",AE17-AD17)</f>
         <v/>
       </c>
-      <c r="AG17" s="12" t="n"/>
-      <c r="AH17" s="12" t="n"/>
+      <c r="AG17" s="12" t="n">
+        <v>0.259736</v>
+      </c>
+      <c r="AH17" s="12" t="n">
+        <v>0.236157</v>
+      </c>
       <c r="AI17" s="13">
         <f>IF(OR(AG17="",AH17=""),"",AH17-AG17)</f>
         <v/>
       </c>
-      <c r="AJ17" s="12" t="n"/>
-      <c r="AK17" s="12" t="n"/>
+      <c r="AJ17" s="12" t="n">
+        <v>0.046572</v>
+      </c>
+      <c r="AK17" s="12" t="n">
+        <v>0.050027</v>
+      </c>
       <c r="AL17" s="13">
         <f>IF(OR(AJ17="",AK17=""),"",AK17-AJ17)</f>
         <v/>
       </c>
-      <c r="AM17" s="10" t="n"/>
-      <c r="AN17" s="10" t="n"/>
+      <c r="AM17" s="10" t="n">
+        <v>4353</v>
+      </c>
+      <c r="AN17" s="10" t="n">
+        <v>4353</v>
+      </c>
       <c r="AO17" s="11">
         <f>IF(OR(AM17="",AN17=""),"",AN17-AM17)</f>
         <v/>
       </c>
-      <c r="AP17" s="10" t="n"/>
-      <c r="AQ17" s="10" t="n"/>
+      <c r="AP17" s="10" t="n">
+        <v>16.182288</v>
+      </c>
+      <c r="AQ17" s="10" t="n">
+        <v>10.844452</v>
+      </c>
       <c r="AR17" s="11">
         <f>IF(OR(AP17="",AQ17=""),"",AQ17-AP17)</f>
         <v/>
       </c>
-      <c r="AS17" s="10" t="n"/>
-      <c r="AT17" s="10" t="n"/>
+      <c r="AS17" s="10" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="AT17" s="10" t="n">
+        <v>26.1</v>
+      </c>
       <c r="AU17" s="11">
         <f>IF(OR(AS17="",AT17=""),"",AT17-AS17)</f>
         <v/>
@@ -2938,92 +3538,152 @@
       <c r="B18" s="9" t="n">
         <v>20260933</v>
       </c>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="C18" s="10" t="n">
+        <v>18329</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>18329</v>
+      </c>
       <c r="E18" s="11">
         <f>IF(OR(C18="",D18=""),"",D18-C18)</f>
         <v/>
       </c>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
+      <c r="F18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H18" s="11">
         <f>IF(OR(F18="",G18=""),"",G18-F18)</f>
         <v/>
       </c>
-      <c r="I18" s="10" t="n"/>
-      <c r="J18" s="10" t="n"/>
+      <c r="I18" s="10" t="n">
+        <v>18122</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>18124</v>
+      </c>
       <c r="K18" s="11">
         <f>IF(OR(I18="",J18=""),"",J18-I18)</f>
         <v/>
       </c>
-      <c r="L18" s="10" t="n"/>
-      <c r="M18" s="10" t="n"/>
+      <c r="L18" s="10" t="n">
+        <v>18329</v>
+      </c>
+      <c r="M18" s="10" t="n">
+        <v>18329</v>
+      </c>
       <c r="N18" s="11">
         <f>IF(OR(L18="",M18=""),"",M18-L18)</f>
         <v/>
       </c>
-      <c r="O18" s="10" t="n"/>
-      <c r="P18" s="10" t="n"/>
+      <c r="O18" s="10" t="n">
+        <v>10.466447</v>
+      </c>
+      <c r="P18" s="10" t="n">
+        <v>7.076308</v>
+      </c>
       <c r="Q18" s="11">
         <f>IF(OR(O18="",P18=""),"",P18-O18)</f>
         <v/>
       </c>
-      <c r="R18" s="10" t="n"/>
-      <c r="S18" s="10" t="n"/>
+      <c r="R18" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="S18" s="10" t="n">
+        <v>17.7</v>
+      </c>
       <c r="T18" s="11">
         <f>IF(OR(R18="",S18=""),"",S18-R18)</f>
         <v/>
       </c>
-      <c r="U18" s="12" t="n"/>
-      <c r="V18" s="12" t="n"/>
+      <c r="U18" s="12" t="n">
+        <v>0.077582</v>
+      </c>
+      <c r="V18" s="12" t="n">
+        <v>0.019805</v>
+      </c>
       <c r="W18" s="13">
         <f>IF(OR(U18="",V18=""),"",V18-U18)</f>
         <v/>
       </c>
-      <c r="X18" s="10" t="n"/>
-      <c r="Y18" s="10" t="n"/>
+      <c r="X18" s="10" t="n">
+        <v>21.264967</v>
+      </c>
+      <c r="Y18" s="10" t="n">
+        <v>14.363561</v>
+      </c>
       <c r="Z18" s="11">
         <f>IF(OR(X18="",Y18=""),"",Y18-X18)</f>
         <v/>
       </c>
-      <c r="AA18" s="10" t="n"/>
-      <c r="AB18" s="10" t="n"/>
+      <c r="AA18" s="10" t="n">
+        <v>232</v>
+      </c>
+      <c r="AB18" s="10" t="n">
+        <v>171</v>
+      </c>
       <c r="AC18" s="11">
         <f>IF(OR(AA18="",AB18=""),"",AB18-AA18)</f>
         <v/>
       </c>
-      <c r="AD18" s="10" t="n"/>
-      <c r="AE18" s="10" t="n"/>
+      <c r="AD18" s="10" t="n">
+        <v>63.380786</v>
+      </c>
+      <c r="AE18" s="10" t="n">
+        <v>65.48078599999999</v>
+      </c>
       <c r="AF18" s="11">
         <f>IF(OR(AD18="",AE18=""),"",AE18-AD18)</f>
         <v/>
       </c>
-      <c r="AG18" s="12" t="n"/>
-      <c r="AH18" s="12" t="n"/>
+      <c r="AG18" s="12" t="n">
+        <v>0.259582</v>
+      </c>
+      <c r="AH18" s="12" t="n">
+        <v>0.236009</v>
+      </c>
       <c r="AI18" s="13">
         <f>IF(OR(AG18="",AH18=""),"",AH18-AG18)</f>
         <v/>
       </c>
-      <c r="AJ18" s="12" t="n"/>
-      <c r="AK18" s="12" t="n"/>
+      <c r="AJ18" s="12" t="n">
+        <v>0.046604</v>
+      </c>
+      <c r="AK18" s="12" t="n">
+        <v>0.05134</v>
+      </c>
       <c r="AL18" s="13">
         <f>IF(OR(AJ18="",AK18=""),"",AK18-AJ18)</f>
         <v/>
       </c>
-      <c r="AM18" s="10" t="n"/>
-      <c r="AN18" s="10" t="n"/>
+      <c r="AM18" s="10" t="n">
+        <v>4370</v>
+      </c>
+      <c r="AN18" s="10" t="n">
+        <v>4370</v>
+      </c>
       <c r="AO18" s="11">
         <f>IF(OR(AM18="",AN18=""),"",AN18-AM18)</f>
         <v/>
       </c>
-      <c r="AP18" s="10" t="n"/>
-      <c r="AQ18" s="10" t="n"/>
+      <c r="AP18" s="10" t="n">
+        <v>15.993776</v>
+      </c>
+      <c r="AQ18" s="10" t="n">
+        <v>10.576064</v>
+      </c>
       <c r="AR18" s="11">
         <f>IF(OR(AP18="",AQ18=""),"",AQ18-AP18)</f>
         <v/>
       </c>
-      <c r="AS18" s="10" t="n"/>
-      <c r="AT18" s="10" t="n"/>
+      <c r="AS18" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT18" s="10" t="n">
+        <v>25.2</v>
+      </c>
       <c r="AU18" s="11">
         <f>IF(OR(AS18="",AT18=""),"",AT18-AS18)</f>
         <v/>
@@ -3036,92 +3696,152 @@
       <c r="B19" s="9" t="n">
         <v>20260934</v>
       </c>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
+      <c r="C19" s="10" t="n">
+        <v>18305</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>18305</v>
+      </c>
       <c r="E19" s="11">
         <f>IF(OR(C19="",D19=""),"",D19-C19)</f>
         <v/>
       </c>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
+      <c r="F19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H19" s="11">
         <f>IF(OR(F19="",G19=""),"",G19-F19)</f>
         <v/>
       </c>
-      <c r="I19" s="10" t="n"/>
-      <c r="J19" s="10" t="n"/>
+      <c r="I19" s="10" t="n">
+        <v>18106</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>18104</v>
+      </c>
       <c r="K19" s="11">
         <f>IF(OR(I19="",J19=""),"",J19-I19)</f>
         <v/>
       </c>
-      <c r="L19" s="10" t="n"/>
-      <c r="M19" s="10" t="n"/>
+      <c r="L19" s="10" t="n">
+        <v>18305</v>
+      </c>
+      <c r="M19" s="10" t="n">
+        <v>18305</v>
+      </c>
       <c r="N19" s="11">
         <f>IF(OR(L19="",M19=""),"",M19-L19)</f>
         <v/>
       </c>
-      <c r="O19" s="10" t="n"/>
-      <c r="P19" s="10" t="n"/>
+      <c r="O19" s="10" t="n">
+        <v>10.745179</v>
+      </c>
+      <c r="P19" s="10" t="n">
+        <v>7.205572</v>
+      </c>
       <c r="Q19" s="11">
         <f>IF(OR(O19="",P19=""),"",P19-O19)</f>
         <v/>
       </c>
-      <c r="R19" s="10" t="n"/>
-      <c r="S19" s="10" t="n"/>
+      <c r="R19" s="10" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="S19" s="10" t="n">
+        <v>18</v>
+      </c>
       <c r="T19" s="11">
         <f>IF(OR(R19="",S19=""),"",S19-R19)</f>
         <v/>
       </c>
-      <c r="U19" s="12" t="n"/>
-      <c r="V19" s="12" t="n"/>
+      <c r="U19" s="12" t="n">
+        <v>0.079323</v>
+      </c>
+      <c r="V19" s="12" t="n">
+        <v>0.0177</v>
+      </c>
       <c r="W19" s="13">
         <f>IF(OR(U19="",V19=""),"",V19-U19)</f>
         <v/>
       </c>
-      <c r="X19" s="10" t="n"/>
-      <c r="Y19" s="10" t="n"/>
+      <c r="X19" s="10" t="n">
+        <v>21.786367</v>
+      </c>
+      <c r="Y19" s="10" t="n">
+        <v>14.598333</v>
+      </c>
       <c r="Z19" s="11">
         <f>IF(OR(X19="",Y19=""),"",Y19-X19)</f>
         <v/>
       </c>
-      <c r="AA19" s="10" t="n"/>
-      <c r="AB19" s="10" t="n"/>
+      <c r="AA19" s="10" t="n">
+        <v>227</v>
+      </c>
+      <c r="AB19" s="10" t="n">
+        <v>169</v>
+      </c>
       <c r="AC19" s="11">
         <f>IF(OR(AA19="",AB19=""),"",AB19-AA19)</f>
         <v/>
       </c>
-      <c r="AD19" s="10" t="n"/>
-      <c r="AE19" s="10" t="n"/>
+      <c r="AD19" s="10" t="n">
+        <v>66.680786</v>
+      </c>
+      <c r="AE19" s="10" t="n">
+        <v>66.680786</v>
+      </c>
       <c r="AF19" s="11">
         <f>IF(OR(AD19="",AE19=""),"",AE19-AD19)</f>
         <v/>
       </c>
-      <c r="AG19" s="12" t="n"/>
-      <c r="AH19" s="12" t="n"/>
+      <c r="AG19" s="12" t="n">
+        <v>0.259127</v>
+      </c>
+      <c r="AH19" s="12" t="n">
+        <v>0.235624</v>
+      </c>
       <c r="AI19" s="13">
         <f>IF(OR(AG19="",AH19=""),"",AH19-AG19)</f>
         <v/>
       </c>
-      <c r="AJ19" s="12" t="n"/>
-      <c r="AK19" s="12" t="n"/>
+      <c r="AJ19" s="12" t="n">
+        <v>0.046491</v>
+      </c>
+      <c r="AK19" s="12" t="n">
+        <v>0.050169</v>
+      </c>
       <c r="AL19" s="13">
         <f>IF(OR(AJ19="",AK19=""),"",AK19-AJ19)</f>
         <v/>
       </c>
-      <c r="AM19" s="10" t="n"/>
-      <c r="AN19" s="10" t="n"/>
+      <c r="AM19" s="10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="AN19" s="10" t="n">
+        <v>4364</v>
+      </c>
       <c r="AO19" s="11">
         <f>IF(OR(AM19="",AN19=""),"",AN19-AM19)</f>
         <v/>
       </c>
-      <c r="AP19" s="10" t="n"/>
-      <c r="AQ19" s="10" t="n"/>
+      <c r="AP19" s="10" t="n">
+        <v>15.850573</v>
+      </c>
+      <c r="AQ19" s="10" t="n">
+        <v>10.35385</v>
+      </c>
       <c r="AR19" s="11">
         <f>IF(OR(AP19="",AQ19=""),"",AQ19-AP19)</f>
         <v/>
       </c>
-      <c r="AS19" s="10" t="n"/>
-      <c r="AT19" s="10" t="n"/>
+      <c r="AS19" s="10" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="AT19" s="10" t="n">
+        <v>24.3</v>
+      </c>
       <c r="AU19" s="11">
         <f>IF(OR(AS19="",AT19=""),"",AT19-AS19)</f>
         <v/>
@@ -3134,92 +3854,152 @@
       <c r="B20" s="9" t="n">
         <v>20260935</v>
       </c>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
+      <c r="C20" s="10" t="n">
+        <v>18293</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>18293</v>
+      </c>
       <c r="E20" s="11">
         <f>IF(OR(C20="",D20=""),"",D20-C20)</f>
         <v/>
       </c>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
+      <c r="F20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H20" s="11">
         <f>IF(OR(F20="",G20=""),"",G20-F20)</f>
         <v/>
       </c>
-      <c r="I20" s="10" t="n"/>
-      <c r="J20" s="10" t="n"/>
+      <c r="I20" s="10" t="n">
+        <v>18090</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>18088</v>
+      </c>
       <c r="K20" s="11">
         <f>IF(OR(I20="",J20=""),"",J20-I20)</f>
         <v/>
       </c>
-      <c r="L20" s="10" t="n"/>
-      <c r="M20" s="10" t="n"/>
+      <c r="L20" s="10" t="n">
+        <v>18293</v>
+      </c>
+      <c r="M20" s="10" t="n">
+        <v>18293</v>
+      </c>
       <c r="N20" s="11">
         <f>IF(OR(L20="",M20=""),"",M20-L20)</f>
         <v/>
       </c>
-      <c r="O20" s="10" t="n"/>
-      <c r="P20" s="10" t="n"/>
+      <c r="O20" s="10" t="n">
+        <v>10.864287</v>
+      </c>
+      <c r="P20" s="10" t="n">
+        <v>7.25302</v>
+      </c>
       <c r="Q20" s="11">
         <f>IF(OR(O20="",P20=""),"",P20-O20)</f>
         <v/>
       </c>
-      <c r="R20" s="10" t="n"/>
-      <c r="S20" s="10" t="n"/>
+      <c r="R20" s="10" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="S20" s="10" t="n">
+        <v>18</v>
+      </c>
       <c r="T20" s="11">
         <f>IF(OR(R20="",S20=""),"",S20-R20)</f>
         <v/>
       </c>
-      <c r="U20" s="12" t="n"/>
-      <c r="V20" s="12" t="n"/>
+      <c r="U20" s="12" t="n">
+        <v>0.083748</v>
+      </c>
+      <c r="V20" s="12" t="n">
+        <v>0.020828</v>
+      </c>
       <c r="W20" s="13">
         <f>IF(OR(U20="",V20=""),"",V20-U20)</f>
         <v/>
       </c>
-      <c r="X20" s="10" t="n"/>
-      <c r="Y20" s="10" t="n"/>
+      <c r="X20" s="10" t="n">
+        <v>22.025933</v>
+      </c>
+      <c r="Y20" s="10" t="n">
+        <v>14.692567</v>
+      </c>
       <c r="Z20" s="11">
         <f>IF(OR(X20="",Y20=""),"",Y20-X20)</f>
         <v/>
       </c>
-      <c r="AA20" s="10" t="n"/>
-      <c r="AB20" s="10" t="n"/>
+      <c r="AA20" s="10" t="n">
+        <v>232</v>
+      </c>
+      <c r="AB20" s="10" t="n">
+        <v>168</v>
+      </c>
       <c r="AC20" s="11">
         <f>IF(OR(AA20="",AB20=""),"",AB20-AA20)</f>
         <v/>
       </c>
-      <c r="AD20" s="10" t="n"/>
-      <c r="AE20" s="10" t="n"/>
+      <c r="AD20" s="10" t="n">
+        <v>68.180786</v>
+      </c>
+      <c r="AE20" s="10" t="n">
+        <v>64.580786</v>
+      </c>
       <c r="AF20" s="11">
         <f>IF(OR(AD20="",AE20=""),"",AE20-AD20)</f>
         <v/>
       </c>
-      <c r="AG20" s="12" t="n"/>
-      <c r="AH20" s="12" t="n"/>
+      <c r="AG20" s="12" t="n">
+        <v>0.259024</v>
+      </c>
+      <c r="AH20" s="12" t="n">
+        <v>0.235487</v>
+      </c>
       <c r="AI20" s="13">
         <f>IF(OR(AG20="",AH20=""),"",AH20-AG20)</f>
         <v/>
       </c>
-      <c r="AJ20" s="12" t="n"/>
-      <c r="AK20" s="12" t="n"/>
+      <c r="AJ20" s="12" t="n">
+        <v>0.046682</v>
+      </c>
+      <c r="AK20" s="12" t="n">
+        <v>0.049597</v>
+      </c>
       <c r="AL20" s="13">
         <f>IF(OR(AJ20="",AK20=""),"",AK20-AJ20)</f>
         <v/>
       </c>
-      <c r="AM20" s="10" t="n"/>
-      <c r="AN20" s="10" t="n"/>
+      <c r="AM20" s="10" t="n">
+        <v>4316</v>
+      </c>
+      <c r="AN20" s="10" t="n">
+        <v>4316</v>
+      </c>
       <c r="AO20" s="11">
         <f>IF(OR(AM20="",AN20=""),"",AN20-AM20)</f>
         <v/>
       </c>
-      <c r="AP20" s="10" t="n"/>
-      <c r="AQ20" s="10" t="n"/>
+      <c r="AP20" s="10" t="n">
+        <v>16.316358</v>
+      </c>
+      <c r="AQ20" s="10" t="n">
+        <v>10.732785</v>
+      </c>
       <c r="AR20" s="11">
         <f>IF(OR(AP20="",AQ20=""),"",AQ20-AP20)</f>
         <v/>
       </c>
-      <c r="AS20" s="10" t="n"/>
-      <c r="AT20" s="10" t="n"/>
+      <c r="AS20" s="10" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="AT20" s="10" t="n">
+        <v>25.8</v>
+      </c>
       <c r="AU20" s="11">
         <f>IF(OR(AS20="",AT20=""),"",AT20-AS20)</f>
         <v/>
@@ -3232,92 +4012,152 @@
       <c r="B21" s="9" t="n">
         <v>20260936</v>
       </c>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
+      <c r="C21" s="10" t="n">
+        <v>18411</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>18411</v>
+      </c>
       <c r="E21" s="11">
         <f>IF(OR(C21="",D21=""),"",D21-C21)</f>
         <v/>
       </c>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
+      <c r="F21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H21" s="11">
         <f>IF(OR(F21="",G21=""),"",G21-F21)</f>
         <v/>
       </c>
-      <c r="I21" s="10" t="n"/>
-      <c r="J21" s="10" t="n"/>
+      <c r="I21" s="10" t="n">
+        <v>18208</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>18208</v>
+      </c>
       <c r="K21" s="11">
         <f>IF(OR(I21="",J21=""),"",J21-I21)</f>
         <v/>
       </c>
-      <c r="L21" s="10" t="n"/>
-      <c r="M21" s="10" t="n"/>
+      <c r="L21" s="10" t="n">
+        <v>18411</v>
+      </c>
+      <c r="M21" s="10" t="n">
+        <v>18411</v>
+      </c>
       <c r="N21" s="11">
         <f>IF(OR(L21="",M21=""),"",M21-L21)</f>
         <v/>
       </c>
-      <c r="O21" s="10" t="n"/>
-      <c r="P21" s="10" t="n"/>
+      <c r="O21" s="10" t="n">
+        <v>10.741046</v>
+      </c>
+      <c r="P21" s="10" t="n">
+        <v>7.353609</v>
+      </c>
       <c r="Q21" s="11">
         <f>IF(OR(O21="",P21=""),"",P21-O21)</f>
         <v/>
       </c>
-      <c r="R21" s="10" t="n"/>
-      <c r="S21" s="10" t="n"/>
+      <c r="R21" s="10" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="S21" s="10" t="n">
+        <v>18.6</v>
+      </c>
       <c r="T21" s="11">
         <f>IF(OR(R21="",S21=""),"",S21-R21)</f>
         <v/>
       </c>
-      <c r="U21" s="12" t="n"/>
-      <c r="V21" s="12" t="n"/>
+      <c r="U21" s="12" t="n">
+        <v>0.084026</v>
+      </c>
+      <c r="V21" s="12" t="n">
+        <v>0.018956</v>
+      </c>
       <c r="W21" s="13">
         <f>IF(OR(U21="",V21=""),"",V21-U21)</f>
         <v/>
       </c>
-      <c r="X21" s="10" t="n"/>
-      <c r="Y21" s="10" t="n"/>
+      <c r="X21" s="10" t="n">
+        <v>21.9107</v>
+      </c>
+      <c r="Y21" s="10" t="n">
+        <v>14.986933</v>
+      </c>
       <c r="Z21" s="11">
         <f>IF(OR(X21="",Y21=""),"",Y21-X21)</f>
         <v/>
       </c>
-      <c r="AA21" s="10" t="n"/>
-      <c r="AB21" s="10" t="n"/>
+      <c r="AA21" s="10" t="n">
+        <v>214</v>
+      </c>
+      <c r="AB21" s="10" t="n">
+        <v>161</v>
+      </c>
       <c r="AC21" s="11">
         <f>IF(OR(AA21="",AB21=""),"",AB21-AA21)</f>
         <v/>
       </c>
-      <c r="AD21" s="10" t="n"/>
-      <c r="AE21" s="10" t="n"/>
+      <c r="AD21" s="10" t="n">
+        <v>63.680786</v>
+      </c>
+      <c r="AE21" s="10" t="n">
+        <v>66.080786</v>
+      </c>
       <c r="AF21" s="11">
         <f>IF(OR(AD21="",AE21=""),"",AE21-AD21)</f>
         <v/>
       </c>
-      <c r="AG21" s="12" t="n"/>
-      <c r="AH21" s="12" t="n"/>
+      <c r="AG21" s="12" t="n">
+        <v>0.260703</v>
+      </c>
+      <c r="AH21" s="12" t="n">
+        <v>0.237011</v>
+      </c>
       <c r="AI21" s="13">
         <f>IF(OR(AG21="",AH21=""),"",AH21-AG21)</f>
         <v/>
       </c>
-      <c r="AJ21" s="12" t="n"/>
-      <c r="AK21" s="12" t="n"/>
+      <c r="AJ21" s="12" t="n">
+        <v>0.046637</v>
+      </c>
+      <c r="AK21" s="12" t="n">
+        <v>0.050189</v>
+      </c>
       <c r="AL21" s="13">
         <f>IF(OR(AJ21="",AK21=""),"",AK21-AJ21)</f>
         <v/>
       </c>
-      <c r="AM21" s="10" t="n"/>
-      <c r="AN21" s="10" t="n"/>
+      <c r="AM21" s="10" t="n">
+        <v>4336</v>
+      </c>
+      <c r="AN21" s="10" t="n">
+        <v>4336</v>
+      </c>
       <c r="AO21" s="11">
         <f>IF(OR(AM21="",AN21=""),"",AN21-AM21)</f>
         <v/>
       </c>
-      <c r="AP21" s="10" t="n"/>
-      <c r="AQ21" s="10" t="n"/>
+      <c r="AP21" s="10" t="n">
+        <v>16.066882</v>
+      </c>
+      <c r="AQ21" s="10" t="n">
+        <v>10.588768</v>
+      </c>
       <c r="AR21" s="11">
         <f>IF(OR(AP21="",AQ21=""),"",AQ21-AP21)</f>
         <v/>
       </c>
-      <c r="AS21" s="10" t="n"/>
-      <c r="AT21" s="10" t="n"/>
+      <c r="AS21" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT21" s="10" t="n">
+        <v>24.6</v>
+      </c>
       <c r="AU21" s="11">
         <f>IF(OR(AS21="",AT21=""),"",AT21-AS21)</f>
         <v/>
@@ -3330,92 +4170,152 @@
       <c r="B22" s="9" t="n">
         <v>20260937</v>
       </c>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
+      <c r="C22" s="10" t="n">
+        <v>18518</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>18518</v>
+      </c>
       <c r="E22" s="11">
         <f>IF(OR(C22="",D22=""),"",D22-C22)</f>
         <v/>
       </c>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
+      <c r="F22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H22" s="11">
         <f>IF(OR(F22="",G22=""),"",G22-F22)</f>
         <v/>
       </c>
-      <c r="I22" s="10" t="n"/>
-      <c r="J22" s="10" t="n"/>
+      <c r="I22" s="10" t="n">
+        <v>18307</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>18305</v>
+      </c>
       <c r="K22" s="11">
         <f>IF(OR(I22="",J22=""),"",J22-I22)</f>
         <v/>
       </c>
-      <c r="L22" s="10" t="n"/>
-      <c r="M22" s="10" t="n"/>
+      <c r="L22" s="10" t="n">
+        <v>18518</v>
+      </c>
+      <c r="M22" s="10" t="n">
+        <v>18518</v>
+      </c>
       <c r="N22" s="11">
         <f>IF(OR(L22="",M22=""),"",M22-L22)</f>
         <v/>
       </c>
-      <c r="O22" s="10" t="n"/>
-      <c r="P22" s="10" t="n"/>
+      <c r="O22" s="10" t="n">
+        <v>11.165272</v>
+      </c>
+      <c r="P22" s="10" t="n">
+        <v>7.514629</v>
+      </c>
       <c r="Q22" s="11">
         <f>IF(OR(O22="",P22=""),"",P22-O22)</f>
         <v/>
       </c>
-      <c r="R22" s="10" t="n"/>
-      <c r="S22" s="10" t="n"/>
+      <c r="R22" s="10" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="S22" s="10" t="n">
+        <v>18.9</v>
+      </c>
       <c r="T22" s="11">
         <f>IF(OR(R22="",S22=""),"",S22-R22)</f>
         <v/>
       </c>
-      <c r="U22" s="12" t="n"/>
-      <c r="V22" s="12" t="n"/>
+      <c r="U22" s="12" t="n">
+        <v>0.090183</v>
+      </c>
+      <c r="V22" s="12" t="n">
+        <v>0.027865</v>
+      </c>
       <c r="W22" s="13">
         <f>IF(OR(U22="",V22=""),"",V22-U22)</f>
         <v/>
       </c>
-      <c r="X22" s="10" t="n"/>
-      <c r="Y22" s="10" t="n"/>
+      <c r="X22" s="10" t="n">
+        <v>22.917633</v>
+      </c>
+      <c r="Y22" s="10" t="n">
+        <v>15.410867</v>
+      </c>
       <c r="Z22" s="11">
         <f>IF(OR(X22="",Y22=""),"",Y22-X22)</f>
         <v/>
       </c>
-      <c r="AA22" s="10" t="n"/>
-      <c r="AB22" s="10" t="n"/>
+      <c r="AA22" s="10" t="n">
+        <v>246</v>
+      </c>
+      <c r="AB22" s="10" t="n">
+        <v>183</v>
+      </c>
       <c r="AC22" s="11">
         <f>IF(OR(AA22="",AB22=""),"",AB22-AA22)</f>
         <v/>
       </c>
-      <c r="AD22" s="10" t="n"/>
-      <c r="AE22" s="10" t="n"/>
+      <c r="AD22" s="10" t="n">
+        <v>67.580786</v>
+      </c>
+      <c r="AE22" s="10" t="n">
+        <v>65.180786</v>
+      </c>
       <c r="AF22" s="11">
         <f>IF(OR(AD22="",AE22=""),"",AE22-AD22)</f>
         <v/>
       </c>
-      <c r="AG22" s="12" t="n"/>
-      <c r="AH22" s="12" t="n"/>
+      <c r="AG22" s="12" t="n">
+        <v>0.262428</v>
+      </c>
+      <c r="AH22" s="12" t="n">
+        <v>0.238615</v>
+      </c>
       <c r="AI22" s="13">
         <f>IF(OR(AG22="",AH22=""),"",AH22-AG22)</f>
         <v/>
       </c>
-      <c r="AJ22" s="12" t="n"/>
-      <c r="AK22" s="12" t="n"/>
+      <c r="AJ22" s="12" t="n">
+        <v>0.049376</v>
+      </c>
+      <c r="AK22" s="12" t="n">
+        <v>0.052154</v>
+      </c>
       <c r="AL22" s="13">
         <f>IF(OR(AJ22="",AK22=""),"",AK22-AJ22)</f>
         <v/>
       </c>
-      <c r="AM22" s="10" t="n"/>
-      <c r="AN22" s="10" t="n"/>
+      <c r="AM22" s="10" t="n">
+        <v>4412</v>
+      </c>
+      <c r="AN22" s="10" t="n">
+        <v>4412</v>
+      </c>
       <c r="AO22" s="11">
         <f>IF(OR(AM22="",AN22=""),"",AN22-AM22)</f>
         <v/>
       </c>
-      <c r="AP22" s="10" t="n"/>
-      <c r="AQ22" s="10" t="n"/>
+      <c r="AP22" s="10" t="n">
+        <v>16.738803</v>
+      </c>
+      <c r="AQ22" s="10" t="n">
+        <v>10.894447</v>
+      </c>
       <c r="AR22" s="11">
         <f>IF(OR(AP22="",AQ22=""),"",AQ22-AP22)</f>
         <v/>
       </c>
-      <c r="AS22" s="10" t="n"/>
-      <c r="AT22" s="10" t="n"/>
+      <c r="AS22" s="10" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="AT22" s="10" t="n">
+        <v>26.1</v>
+      </c>
       <c r="AU22" s="11">
         <f>IF(OR(AS22="",AT22=""),"",AT22-AS22)</f>
         <v/>
@@ -3428,92 +4328,152 @@
       <c r="B23" s="9" t="n">
         <v>20260938</v>
       </c>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
+      <c r="C23" s="10" t="n">
+        <v>18395</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>18395</v>
+      </c>
       <c r="E23" s="11">
         <f>IF(OR(C23="",D23=""),"",D23-C23)</f>
         <v/>
       </c>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="10" t="n"/>
+      <c r="F23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H23" s="11">
         <f>IF(OR(F23="",G23=""),"",G23-F23)</f>
         <v/>
       </c>
-      <c r="I23" s="10" t="n"/>
-      <c r="J23" s="10" t="n"/>
+      <c r="I23" s="10" t="n">
+        <v>18179</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>18181</v>
+      </c>
       <c r="K23" s="11">
         <f>IF(OR(I23="",J23=""),"",J23-I23)</f>
         <v/>
       </c>
-      <c r="L23" s="10" t="n"/>
-      <c r="M23" s="10" t="n"/>
+      <c r="L23" s="10" t="n">
+        <v>18395</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>18395</v>
+      </c>
       <c r="N23" s="11">
         <f>IF(OR(L23="",M23=""),"",M23-L23)</f>
         <v/>
       </c>
-      <c r="O23" s="10" t="n"/>
-      <c r="P23" s="10" t="n"/>
+      <c r="O23" s="10" t="n">
+        <v>10.909986</v>
+      </c>
+      <c r="P23" s="10" t="n">
+        <v>7.424034</v>
+      </c>
       <c r="Q23" s="11">
         <f>IF(OR(O23="",P23=""),"",P23-O23)</f>
         <v/>
       </c>
-      <c r="R23" s="10" t="n"/>
-      <c r="S23" s="10" t="n"/>
+      <c r="R23" s="10" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="S23" s="10" t="n">
+        <v>18.6</v>
+      </c>
       <c r="T23" s="11">
         <f>IF(OR(R23="",S23=""),"",S23-R23)</f>
         <v/>
       </c>
-      <c r="U23" s="12" t="n"/>
-      <c r="V23" s="12" t="n"/>
+      <c r="U23" s="12" t="n">
+        <v>0.086491</v>
+      </c>
+      <c r="V23" s="12" t="n">
+        <v>0.02131</v>
+      </c>
       <c r="W23" s="13">
         <f>IF(OR(U23="",V23=""),"",V23-U23)</f>
         <v/>
       </c>
-      <c r="X23" s="10" t="n"/>
-      <c r="Y23" s="10" t="n"/>
+      <c r="X23" s="10" t="n">
+        <v>22.230267</v>
+      </c>
+      <c r="Y23" s="10" t="n">
+        <v>15.116667</v>
+      </c>
       <c r="Z23" s="11">
         <f>IF(OR(X23="",Y23=""),"",Y23-X23)</f>
         <v/>
       </c>
-      <c r="AA23" s="10" t="n"/>
-      <c r="AB23" s="10" t="n"/>
+      <c r="AA23" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB23" s="10" t="n">
+        <v>175</v>
+      </c>
       <c r="AC23" s="11">
         <f>IF(OR(AA23="",AB23=""),"",AB23-AA23)</f>
         <v/>
       </c>
-      <c r="AD23" s="10" t="n"/>
-      <c r="AE23" s="10" t="n"/>
+      <c r="AD23" s="10" t="n">
+        <v>65.48078599999999</v>
+      </c>
+      <c r="AE23" s="10" t="n">
+        <v>63.380786</v>
+      </c>
       <c r="AF23" s="11">
         <f>IF(OR(AD23="",AE23=""),"",AE23-AD23)</f>
         <v/>
       </c>
-      <c r="AG23" s="12" t="n"/>
-      <c r="AH23" s="12" t="n"/>
+      <c r="AG23" s="12" t="n">
+        <v>0.260084</v>
+      </c>
+      <c r="AH23" s="12" t="n">
+        <v>0.236475</v>
+      </c>
       <c r="AI23" s="13">
         <f>IF(OR(AG23="",AH23=""),"",AH23-AG23)</f>
         <v/>
       </c>
-      <c r="AJ23" s="12" t="n"/>
-      <c r="AK23" s="12" t="n"/>
+      <c r="AJ23" s="12" t="n">
+        <v>0.046484</v>
+      </c>
+      <c r="AK23" s="12" t="n">
+        <v>0.050487</v>
+      </c>
       <c r="AL23" s="13">
         <f>IF(OR(AJ23="",AK23=""),"",AK23-AJ23)</f>
         <v/>
       </c>
-      <c r="AM23" s="10" t="n"/>
-      <c r="AN23" s="10" t="n"/>
+      <c r="AM23" s="10" t="n">
+        <v>4331</v>
+      </c>
+      <c r="AN23" s="10" t="n">
+        <v>4331</v>
+      </c>
       <c r="AO23" s="11">
         <f>IF(OR(AM23="",AN23=""),"",AN23-AM23)</f>
         <v/>
       </c>
-      <c r="AP23" s="10" t="n"/>
-      <c r="AQ23" s="10" t="n"/>
+      <c r="AP23" s="10" t="n">
+        <v>16.424567</v>
+      </c>
+      <c r="AQ23" s="10" t="n">
+        <v>11.06786</v>
+      </c>
       <c r="AR23" s="11">
         <f>IF(OR(AP23="",AQ23=""),"",AQ23-AP23)</f>
         <v/>
       </c>
-      <c r="AS23" s="10" t="n"/>
-      <c r="AT23" s="10" t="n"/>
+      <c r="AS23" s="10" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="AT23" s="10" t="n">
+        <v>26.4</v>
+      </c>
       <c r="AU23" s="11">
         <f>IF(OR(AS23="",AT23=""),"",AT23-AS23)</f>
         <v/>
@@ -3526,92 +4486,152 @@
       <c r="B24" s="9" t="n">
         <v>20260939</v>
       </c>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
+      <c r="C24" s="10" t="n">
+        <v>18393</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>18393</v>
+      </c>
       <c r="E24" s="11">
         <f>IF(OR(C24="",D24=""),"",D24-C24)</f>
         <v/>
       </c>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
+      <c r="F24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H24" s="11">
         <f>IF(OR(F24="",G24=""),"",G24-F24)</f>
         <v/>
       </c>
-      <c r="I24" s="10" t="n"/>
-      <c r="J24" s="10" t="n"/>
+      <c r="I24" s="10" t="n">
+        <v>18183</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>18186</v>
+      </c>
       <c r="K24" s="11">
         <f>IF(OR(I24="",J24=""),"",J24-I24)</f>
         <v/>
       </c>
-      <c r="L24" s="10" t="n"/>
-      <c r="M24" s="10" t="n"/>
+      <c r="L24" s="10" t="n">
+        <v>18393</v>
+      </c>
+      <c r="M24" s="10" t="n">
+        <v>18393</v>
+      </c>
       <c r="N24" s="11">
         <f>IF(OR(L24="",M24=""),"",M24-L24)</f>
         <v/>
       </c>
-      <c r="O24" s="10" t="n"/>
-      <c r="P24" s="10" t="n"/>
+      <c r="O24" s="10" t="n">
+        <v>10.781259</v>
+      </c>
+      <c r="P24" s="10" t="n">
+        <v>7.416392</v>
+      </c>
       <c r="Q24" s="11">
         <f>IF(OR(O24="",P24=""),"",P24-O24)</f>
         <v/>
       </c>
-      <c r="R24" s="10" t="n"/>
-      <c r="S24" s="10" t="n"/>
+      <c r="R24" s="10" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="S24" s="10" t="n">
+        <v>18.3</v>
+      </c>
       <c r="T24" s="11">
         <f>IF(OR(R24="",S24=""),"",S24-R24)</f>
         <v/>
       </c>
-      <c r="U24" s="12" t="n"/>
-      <c r="V24" s="12" t="n"/>
+      <c r="U24" s="12" t="n">
+        <v>0.08122699999999999</v>
+      </c>
+      <c r="V24" s="12" t="n">
+        <v>0.022998</v>
+      </c>
       <c r="W24" s="13">
         <f>IF(OR(U24="",V24=""),"",V24-U24)</f>
         <v/>
       </c>
-      <c r="X24" s="10" t="n"/>
-      <c r="Y24" s="10" t="n"/>
+      <c r="X24" s="10" t="n">
+        <v>21.971467</v>
+      </c>
+      <c r="Y24" s="10" t="n">
+        <v>15.103067</v>
+      </c>
       <c r="Z24" s="11">
         <f>IF(OR(X24="",Y24=""),"",Y24-X24)</f>
         <v/>
       </c>
-      <c r="AA24" s="10" t="n"/>
-      <c r="AB24" s="10" t="n"/>
+      <c r="AA24" s="10" t="n">
+        <v>236</v>
+      </c>
+      <c r="AB24" s="10" t="n">
+        <v>177</v>
+      </c>
       <c r="AC24" s="11">
         <f>IF(OR(AA24="",AB24=""),"",AB24-AA24)</f>
         <v/>
       </c>
-      <c r="AD24" s="10" t="n"/>
-      <c r="AE24" s="10" t="n"/>
+      <c r="AD24" s="10" t="n">
+        <v>65.48078599999999</v>
+      </c>
+      <c r="AE24" s="10" t="n">
+        <v>62.180786</v>
+      </c>
       <c r="AF24" s="11">
         <f>IF(OR(AD24="",AE24=""),"",AE24-AD24)</f>
         <v/>
       </c>
-      <c r="AG24" s="12" t="n"/>
-      <c r="AH24" s="12" t="n"/>
+      <c r="AG24" s="12" t="n">
+        <v>0.26035</v>
+      </c>
+      <c r="AH24" s="12" t="n">
+        <v>0.236706</v>
+      </c>
       <c r="AI24" s="13">
         <f>IF(OR(AG24="",AH24=""),"",AH24-AG24)</f>
         <v/>
       </c>
-      <c r="AJ24" s="12" t="n"/>
-      <c r="AK24" s="12" t="n"/>
+      <c r="AJ24" s="12" t="n">
+        <v>0.047594</v>
+      </c>
+      <c r="AK24" s="12" t="n">
+        <v>0.050766</v>
+      </c>
       <c r="AL24" s="13">
         <f>IF(OR(AJ24="",AK24=""),"",AK24-AJ24)</f>
         <v/>
       </c>
-      <c r="AM24" s="10" t="n"/>
-      <c r="AN24" s="10" t="n"/>
+      <c r="AM24" s="10" t="n">
+        <v>4386</v>
+      </c>
+      <c r="AN24" s="10" t="n">
+        <v>4386</v>
+      </c>
       <c r="AO24" s="11">
         <f>IF(OR(AM24="",AN24=""),"",AN24-AM24)</f>
         <v/>
       </c>
-      <c r="AP24" s="10" t="n"/>
-      <c r="AQ24" s="10" t="n"/>
+      <c r="AP24" s="10" t="n">
+        <v>15.927223</v>
+      </c>
+      <c r="AQ24" s="10" t="n">
+        <v>10.712038</v>
+      </c>
       <c r="AR24" s="11">
         <f>IF(OR(AP24="",AQ24=""),"",AQ24-AP24)</f>
         <v/>
       </c>
-      <c r="AS24" s="10" t="n"/>
-      <c r="AT24" s="10" t="n"/>
+      <c r="AS24" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT24" s="10" t="n">
+        <v>25.2</v>
+      </c>
       <c r="AU24" s="11">
         <f>IF(OR(AS24="",AT24=""),"",AT24-AS24)</f>
         <v/>
@@ -3624,92 +4644,152 @@
       <c r="B25" s="9" t="n">
         <v>20260940</v>
       </c>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
+      <c r="C25" s="10" t="n">
+        <v>18390</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>18390</v>
+      </c>
       <c r="E25" s="11">
         <f>IF(OR(C25="",D25=""),"",D25-C25)</f>
         <v/>
       </c>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10" t="n"/>
+      <c r="F25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H25" s="11">
         <f>IF(OR(F25="",G25=""),"",G25-F25)</f>
         <v/>
       </c>
-      <c r="I25" s="10" t="n"/>
-      <c r="J25" s="10" t="n"/>
+      <c r="I25" s="10" t="n">
+        <v>18193</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>18188</v>
+      </c>
       <c r="K25" s="11">
         <f>IF(OR(I25="",J25=""),"",J25-I25)</f>
         <v/>
       </c>
-      <c r="L25" s="10" t="n"/>
-      <c r="M25" s="10" t="n"/>
+      <c r="L25" s="10" t="n">
+        <v>18390</v>
+      </c>
+      <c r="M25" s="10" t="n">
+        <v>18390</v>
+      </c>
       <c r="N25" s="11">
         <f>IF(OR(L25="",M25=""),"",M25-L25)</f>
         <v/>
       </c>
-      <c r="O25" s="10" t="n"/>
-      <c r="P25" s="10" t="n"/>
+      <c r="O25" s="10" t="n">
+        <v>10.77075</v>
+      </c>
+      <c r="P25" s="10" t="n">
+        <v>7.244535</v>
+      </c>
       <c r="Q25" s="11">
         <f>IF(OR(O25="",P25=""),"",P25-O25)</f>
         <v/>
       </c>
-      <c r="R25" s="10" t="n"/>
-      <c r="S25" s="10" t="n"/>
+      <c r="R25" s="10" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="S25" s="10" t="n">
+        <v>18</v>
+      </c>
       <c r="T25" s="11">
         <f>IF(OR(R25="",S25=""),"",S25-R25)</f>
         <v/>
       </c>
-      <c r="U25" s="12" t="n"/>
-      <c r="V25" s="12" t="n"/>
+      <c r="U25" s="12" t="n">
+        <v>0.081349</v>
+      </c>
+      <c r="V25" s="12" t="n">
+        <v>0.016368</v>
+      </c>
       <c r="W25" s="13">
         <f>IF(OR(U25="",V25=""),"",V25-U25)</f>
         <v/>
       </c>
-      <c r="X25" s="10" t="n"/>
-      <c r="Y25" s="10" t="n"/>
+      <c r="X25" s="10" t="n">
+        <v>21.957167</v>
+      </c>
+      <c r="Y25" s="10" t="n">
+        <v>14.754533</v>
+      </c>
       <c r="Z25" s="11">
         <f>IF(OR(X25="",Y25=""),"",Y25-X25)</f>
         <v/>
       </c>
-      <c r="AA25" s="10" t="n"/>
-      <c r="AB25" s="10" t="n"/>
+      <c r="AA25" s="10" t="n">
+        <v>224</v>
+      </c>
+      <c r="AB25" s="10" t="n">
+        <v>162</v>
+      </c>
       <c r="AC25" s="11">
         <f>IF(OR(AA25="",AB25=""),"",AB25-AA25)</f>
         <v/>
       </c>
-      <c r="AD25" s="10" t="n"/>
-      <c r="AE25" s="10" t="n"/>
+      <c r="AD25" s="10" t="n">
+        <v>67.28078600000001</v>
+      </c>
+      <c r="AE25" s="10" t="n">
+        <v>63.980786</v>
+      </c>
       <c r="AF25" s="11">
         <f>IF(OR(AD25="",AE25=""),"",AE25-AD25)</f>
         <v/>
       </c>
-      <c r="AG25" s="12" t="n"/>
-      <c r="AH25" s="12" t="n"/>
+      <c r="AG25" s="12" t="n">
+        <v>0.260789</v>
+      </c>
+      <c r="AH25" s="12" t="n">
+        <v>0.237117</v>
+      </c>
       <c r="AI25" s="13">
         <f>IF(OR(AG25="",AH25=""),"",AH25-AG25)</f>
         <v/>
       </c>
-      <c r="AJ25" s="12" t="n"/>
-      <c r="AK25" s="12" t="n"/>
+      <c r="AJ25" s="12" t="n">
+        <v>0.048033</v>
+      </c>
+      <c r="AK25" s="12" t="n">
+        <v>0.051446</v>
+      </c>
       <c r="AL25" s="13">
         <f>IF(OR(AJ25="",AK25=""),"",AK25-AJ25)</f>
         <v/>
       </c>
-      <c r="AM25" s="10" t="n"/>
-      <c r="AN25" s="10" t="n"/>
+      <c r="AM25" s="10" t="n">
+        <v>4329</v>
+      </c>
+      <c r="AN25" s="10" t="n">
+        <v>4329</v>
+      </c>
       <c r="AO25" s="11">
         <f>IF(OR(AM25="",AN25=""),"",AN25-AM25)</f>
         <v/>
       </c>
-      <c r="AP25" s="10" t="n"/>
-      <c r="AQ25" s="10" t="n"/>
+      <c r="AP25" s="10" t="n">
+        <v>16.02176</v>
+      </c>
+      <c r="AQ25" s="10" t="n">
+        <v>10.651767</v>
+      </c>
       <c r="AR25" s="11">
         <f>IF(OR(AP25="",AQ25=""),"",AQ25-AP25)</f>
         <v/>
       </c>
-      <c r="AS25" s="10" t="n"/>
-      <c r="AT25" s="10" t="n"/>
+      <c r="AS25" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT25" s="10" t="n">
+        <v>24.6</v>
+      </c>
       <c r="AU25" s="11">
         <f>IF(OR(AS25="",AT25=""),"",AT25-AS25)</f>
         <v/>
@@ -3722,92 +4802,152 @@
       <c r="B26" s="9" t="n">
         <v>20260941</v>
       </c>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="10" t="n"/>
+      <c r="C26" s="10" t="n">
+        <v>18346</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>18346</v>
+      </c>
       <c r="E26" s="11">
         <f>IF(OR(C26="",D26=""),"",D26-C26)</f>
         <v/>
       </c>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="10" t="n"/>
+      <c r="F26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H26" s="11">
         <f>IF(OR(F26="",G26=""),"",G26-F26)</f>
         <v/>
       </c>
-      <c r="I26" s="10" t="n"/>
-      <c r="J26" s="10" t="n"/>
+      <c r="I26" s="10" t="n">
+        <v>18142</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>18145</v>
+      </c>
       <c r="K26" s="11">
         <f>IF(OR(I26="",J26=""),"",J26-I26)</f>
         <v/>
       </c>
-      <c r="L26" s="10" t="n"/>
-      <c r="M26" s="10" t="n"/>
+      <c r="L26" s="10" t="n">
+        <v>18346</v>
+      </c>
+      <c r="M26" s="10" t="n">
+        <v>18346</v>
+      </c>
       <c r="N26" s="11">
         <f>IF(OR(L26="",M26=""),"",M26-L26)</f>
         <v/>
       </c>
-      <c r="O26" s="10" t="n"/>
-      <c r="P26" s="10" t="n"/>
+      <c r="O26" s="10" t="n">
+        <v>10.734558</v>
+      </c>
+      <c r="P26" s="10" t="n">
+        <v>7.33095</v>
+      </c>
       <c r="Q26" s="11">
         <f>IF(OR(O26="",P26=""),"",P26-O26)</f>
         <v/>
       </c>
-      <c r="R26" s="10" t="n"/>
-      <c r="S26" s="10" t="n"/>
+      <c r="R26" s="10" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="S26" s="10" t="n">
+        <v>18.3</v>
+      </c>
       <c r="T26" s="11">
         <f>IF(OR(R26="",S26=""),"",S26-R26)</f>
         <v/>
       </c>
-      <c r="U26" s="12" t="n"/>
-      <c r="V26" s="12" t="n"/>
+      <c r="U26" s="12" t="n">
+        <v>0.083288</v>
+      </c>
+      <c r="V26" s="12" t="n">
+        <v>0.019132</v>
+      </c>
       <c r="W26" s="13">
         <f>IF(OR(U26="",V26=""),"",V26-U26)</f>
         <v/>
       </c>
-      <c r="X26" s="10" t="n"/>
-      <c r="Y26" s="10" t="n"/>
+      <c r="X26" s="10" t="n">
+        <v>21.822633</v>
+      </c>
+      <c r="Y26" s="10" t="n">
+        <v>14.900367</v>
+      </c>
       <c r="Z26" s="11">
         <f>IF(OR(X26="",Y26=""),"",Y26-X26)</f>
         <v/>
       </c>
-      <c r="AA26" s="10" t="n"/>
-      <c r="AB26" s="10" t="n"/>
+      <c r="AA26" s="10" t="n">
+        <v>214</v>
+      </c>
+      <c r="AB26" s="10" t="n">
+        <v>160</v>
+      </c>
       <c r="AC26" s="11">
         <f>IF(OR(AA26="",AB26=""),"",AB26-AA26)</f>
         <v/>
       </c>
-      <c r="AD26" s="10" t="n"/>
-      <c r="AE26" s="10" t="n"/>
+      <c r="AD26" s="10" t="n">
+        <v>64.580786</v>
+      </c>
+      <c r="AE26" s="10" t="n">
+        <v>63.080786</v>
+      </c>
       <c r="AF26" s="11">
         <f>IF(OR(AD26="",AE26=""),"",AE26-AD26)</f>
         <v/>
       </c>
-      <c r="AG26" s="12" t="n"/>
-      <c r="AH26" s="12" t="n"/>
+      <c r="AG26" s="12" t="n">
+        <v>0.259418</v>
+      </c>
+      <c r="AH26" s="12" t="n">
+        <v>0.235924</v>
+      </c>
       <c r="AI26" s="13">
         <f>IF(OR(AG26="",AH26=""),"",AH26-AG26)</f>
         <v/>
       </c>
-      <c r="AJ26" s="12" t="n"/>
-      <c r="AK26" s="12" t="n"/>
+      <c r="AJ26" s="12" t="n">
+        <v>0.046653</v>
+      </c>
+      <c r="AK26" s="12" t="n">
+        <v>0.050332</v>
+      </c>
       <c r="AL26" s="13">
         <f>IF(OR(AJ26="",AK26=""),"",AK26-AJ26)</f>
         <v/>
       </c>
-      <c r="AM26" s="10" t="n"/>
-      <c r="AN26" s="10" t="n"/>
+      <c r="AM26" s="10" t="n">
+        <v>4343</v>
+      </c>
+      <c r="AN26" s="10" t="n">
+        <v>4343</v>
+      </c>
       <c r="AO26" s="11">
         <f>IF(OR(AM26="",AN26=""),"",AN26-AM26)</f>
         <v/>
       </c>
-      <c r="AP26" s="10" t="n"/>
-      <c r="AQ26" s="10" t="n"/>
+      <c r="AP26" s="10" t="n">
+        <v>15.670873</v>
+      </c>
+      <c r="AQ26" s="10" t="n">
+        <v>10.509118</v>
+      </c>
       <c r="AR26" s="11">
         <f>IF(OR(AP26="",AQ26=""),"",AQ26-AP26)</f>
         <v/>
       </c>
-      <c r="AS26" s="10" t="n"/>
-      <c r="AT26" s="10" t="n"/>
+      <c r="AS26" s="10" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="AT26" s="10" t="n">
+        <v>24.6</v>
+      </c>
       <c r="AU26" s="11">
         <f>IF(OR(AS26="",AT26=""),"",AT26-AS26)</f>
         <v/>
@@ -3820,92 +4960,152 @@
       <c r="B27" s="9" t="n">
         <v>20260942</v>
       </c>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="10" t="n"/>
+      <c r="C27" s="10" t="n">
+        <v>18375</v>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>18375</v>
+      </c>
       <c r="E27" s="11">
         <f>IF(OR(C27="",D27=""),"",D27-C27)</f>
         <v/>
       </c>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="10" t="n"/>
+      <c r="F27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H27" s="11">
         <f>IF(OR(F27="",G27=""),"",G27-F27)</f>
         <v/>
       </c>
-      <c r="I27" s="10" t="n"/>
-      <c r="J27" s="10" t="n"/>
+      <c r="I27" s="10" t="n">
+        <v>18154</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>18163</v>
+      </c>
       <c r="K27" s="11">
         <f>IF(OR(I27="",J27=""),"",J27-I27)</f>
         <v/>
       </c>
-      <c r="L27" s="10" t="n"/>
-      <c r="M27" s="10" t="n"/>
+      <c r="L27" s="10" t="n">
+        <v>18375</v>
+      </c>
+      <c r="M27" s="10" t="n">
+        <v>18375</v>
+      </c>
       <c r="N27" s="11">
         <f>IF(OR(L27="",M27=""),"",M27-L27)</f>
         <v/>
       </c>
-      <c r="O27" s="10" t="n"/>
-      <c r="P27" s="10" t="n"/>
+      <c r="O27" s="10" t="n">
+        <v>10.598988</v>
+      </c>
+      <c r="P27" s="10" t="n">
+        <v>7.246253</v>
+      </c>
       <c r="Q27" s="11">
         <f>IF(OR(O27="",P27=""),"",P27-O27)</f>
         <v/>
       </c>
-      <c r="R27" s="10" t="n"/>
-      <c r="S27" s="10" t="n"/>
+      <c r="R27" s="10" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="S27" s="10" t="n">
+        <v>18.3</v>
+      </c>
       <c r="T27" s="11">
         <f>IF(OR(R27="",S27=""),"",S27-R27)</f>
         <v/>
       </c>
-      <c r="U27" s="12" t="n"/>
-      <c r="V27" s="12" t="n"/>
+      <c r="U27" s="12" t="n">
+        <v>0.083102</v>
+      </c>
+      <c r="V27" s="12" t="n">
+        <v>0.018884</v>
+      </c>
       <c r="W27" s="13">
         <f>IF(OR(U27="",V27=""),"",V27-U27)</f>
         <v/>
       </c>
-      <c r="X27" s="10" t="n"/>
-      <c r="Y27" s="10" t="n"/>
+      <c r="X27" s="10" t="n">
+        <v>21.579767</v>
+      </c>
+      <c r="Y27" s="10" t="n">
+        <v>14.744067</v>
+      </c>
       <c r="Z27" s="11">
         <f>IF(OR(X27="",Y27=""),"",Y27-X27)</f>
         <v/>
       </c>
-      <c r="AA27" s="10" t="n"/>
-      <c r="AB27" s="10" t="n"/>
+      <c r="AA27" s="10" t="n">
+        <v>218</v>
+      </c>
+      <c r="AB27" s="10" t="n">
+        <v>156</v>
+      </c>
       <c r="AC27" s="11">
         <f>IF(OR(AA27="",AB27=""),"",AB27-AA27)</f>
         <v/>
       </c>
-      <c r="AD27" s="10" t="n"/>
-      <c r="AE27" s="10" t="n"/>
+      <c r="AD27" s="10" t="n">
+        <v>67.28078600000001</v>
+      </c>
+      <c r="AE27" s="10" t="n">
+        <v>63.380786</v>
+      </c>
       <c r="AF27" s="11">
         <f>IF(OR(AD27="",AE27=""),"",AE27-AD27)</f>
         <v/>
       </c>
-      <c r="AG27" s="12" t="n"/>
-      <c r="AH27" s="12" t="n"/>
+      <c r="AG27" s="12" t="n">
+        <v>0.259789</v>
+      </c>
+      <c r="AH27" s="12" t="n">
+        <v>0.236247</v>
+      </c>
       <c r="AI27" s="13">
         <f>IF(OR(AG27="",AH27=""),"",AH27-AG27)</f>
         <v/>
       </c>
-      <c r="AJ27" s="12" t="n"/>
-      <c r="AK27" s="12" t="n"/>
+      <c r="AJ27" s="12" t="n">
+        <v>0.04732</v>
+      </c>
+      <c r="AK27" s="12" t="n">
+        <v>0.050679</v>
+      </c>
       <c r="AL27" s="13">
         <f>IF(OR(AJ27="",AK27=""),"",AK27-AJ27)</f>
         <v/>
       </c>
-      <c r="AM27" s="10" t="n"/>
-      <c r="AN27" s="10" t="n"/>
+      <c r="AM27" s="10" t="n">
+        <v>4376</v>
+      </c>
+      <c r="AN27" s="10" t="n">
+        <v>4376</v>
+      </c>
       <c r="AO27" s="11">
         <f>IF(OR(AM27="",AN27=""),"",AN27-AM27)</f>
         <v/>
       </c>
-      <c r="AP27" s="10" t="n"/>
-      <c r="AQ27" s="10" t="n"/>
+      <c r="AP27" s="10" t="n">
+        <v>16.028953</v>
+      </c>
+      <c r="AQ27" s="10" t="n">
+        <v>10.552994</v>
+      </c>
       <c r="AR27" s="11">
         <f>IF(OR(AP27="",AQ27=""),"",AQ27-AP27)</f>
         <v/>
       </c>
-      <c r="AS27" s="10" t="n"/>
-      <c r="AT27" s="10" t="n"/>
+      <c r="AS27" s="10" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="AT27" s="10" t="n">
+        <v>24.9</v>
+      </c>
       <c r="AU27" s="11">
         <f>IF(OR(AS27="",AT27=""),"",AT27-AS27)</f>
         <v/>
@@ -3918,92 +5118,152 @@
       <c r="B28" s="9" t="n">
         <v>20260943</v>
       </c>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
+      <c r="C28" s="10" t="n">
+        <v>18514</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>18514</v>
+      </c>
       <c r="E28" s="11">
         <f>IF(OR(C28="",D28=""),"",D28-C28)</f>
         <v/>
       </c>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
+      <c r="F28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H28" s="11">
         <f>IF(OR(F28="",G28=""),"",G28-F28)</f>
         <v/>
       </c>
-      <c r="I28" s="10" t="n"/>
-      <c r="J28" s="10" t="n"/>
+      <c r="I28" s="10" t="n">
+        <v>18312</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>18316</v>
+      </c>
       <c r="K28" s="11">
         <f>IF(OR(I28="",J28=""),"",J28-I28)</f>
         <v/>
       </c>
-      <c r="L28" s="10" t="n"/>
-      <c r="M28" s="10" t="n"/>
+      <c r="L28" s="10" t="n">
+        <v>18514</v>
+      </c>
+      <c r="M28" s="10" t="n">
+        <v>18514</v>
+      </c>
       <c r="N28" s="11">
         <f>IF(OR(L28="",M28=""),"",M28-L28)</f>
         <v/>
       </c>
-      <c r="O28" s="10" t="n"/>
-      <c r="P28" s="10" t="n"/>
+      <c r="O28" s="10" t="n">
+        <v>10.99563</v>
+      </c>
+      <c r="P28" s="10" t="n">
+        <v>7.452976</v>
+      </c>
       <c r="Q28" s="11">
         <f>IF(OR(O28="",P28=""),"",P28-O28)</f>
         <v/>
       </c>
-      <c r="R28" s="10" t="n"/>
-      <c r="S28" s="10" t="n"/>
+      <c r="R28" s="10" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="S28" s="10" t="n">
+        <v>18.9</v>
+      </c>
       <c r="T28" s="11">
         <f>IF(OR(R28="",S28=""),"",S28-R28)</f>
         <v/>
       </c>
-      <c r="U28" s="12" t="n"/>
-      <c r="V28" s="12" t="n"/>
+      <c r="U28" s="12" t="n">
+        <v>0.089392</v>
+      </c>
+      <c r="V28" s="12" t="n">
+        <v>0.021767</v>
+      </c>
       <c r="W28" s="13">
         <f>IF(OR(U28="",V28=""),"",V28-U28)</f>
         <v/>
       </c>
-      <c r="X28" s="10" t="n"/>
-      <c r="Y28" s="10" t="n"/>
+      <c r="X28" s="10" t="n">
+        <v>22.570433</v>
+      </c>
+      <c r="Y28" s="10" t="n">
+        <v>15.2865</v>
+      </c>
       <c r="Z28" s="11">
         <f>IF(OR(X28="",Y28=""),"",Y28-X28)</f>
         <v/>
       </c>
-      <c r="AA28" s="10" t="n"/>
-      <c r="AB28" s="10" t="n"/>
+      <c r="AA28" s="10" t="n">
+        <v>234</v>
+      </c>
+      <c r="AB28" s="10" t="n">
+        <v>168</v>
+      </c>
       <c r="AC28" s="11">
         <f>IF(OR(AA28="",AB28=""),"",AB28-AA28)</f>
         <v/>
       </c>
-      <c r="AD28" s="10" t="n"/>
-      <c r="AE28" s="10" t="n"/>
+      <c r="AD28" s="10" t="n">
+        <v>63.980786</v>
+      </c>
+      <c r="AE28" s="10" t="n">
+        <v>64.880786</v>
+      </c>
       <c r="AF28" s="11">
         <f>IF(OR(AD28="",AE28=""),"",AE28-AD28)</f>
         <v/>
       </c>
-      <c r="AG28" s="12" t="n"/>
-      <c r="AH28" s="12" t="n"/>
+      <c r="AG28" s="12" t="n">
+        <v>0.262274</v>
+      </c>
+      <c r="AH28" s="12" t="n">
+        <v>0.238455</v>
+      </c>
       <c r="AI28" s="13">
         <f>IF(OR(AG28="",AH28=""),"",AH28-AG28)</f>
         <v/>
       </c>
-      <c r="AJ28" s="12" t="n"/>
-      <c r="AK28" s="12" t="n"/>
+      <c r="AJ28" s="12" t="n">
+        <v>0.047797</v>
+      </c>
+      <c r="AK28" s="12" t="n">
+        <v>0.052307</v>
+      </c>
       <c r="AL28" s="13">
         <f>IF(OR(AJ28="",AK28=""),"",AK28-AJ28)</f>
         <v/>
       </c>
-      <c r="AM28" s="10" t="n"/>
-      <c r="AN28" s="10" t="n"/>
+      <c r="AM28" s="10" t="n">
+        <v>4385</v>
+      </c>
+      <c r="AN28" s="10" t="n">
+        <v>4385</v>
+      </c>
       <c r="AO28" s="11">
         <f>IF(OR(AM28="",AN28=""),"",AN28-AM28)</f>
         <v/>
       </c>
-      <c r="AP28" s="10" t="n"/>
-      <c r="AQ28" s="10" t="n"/>
+      <c r="AP28" s="10" t="n">
+        <v>16.715644</v>
+      </c>
+      <c r="AQ28" s="10" t="n">
+        <v>10.982463</v>
+      </c>
       <c r="AR28" s="11">
         <f>IF(OR(AP28="",AQ28=""),"",AQ28-AP28)</f>
         <v/>
       </c>
-      <c r="AS28" s="10" t="n"/>
-      <c r="AT28" s="10" t="n"/>
+      <c r="AS28" s="10" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="AT28" s="10" t="n">
+        <v>26.1</v>
+      </c>
       <c r="AU28" s="11">
         <f>IF(OR(AS28="",AT28=""),"",AT28-AS28)</f>
         <v/>
@@ -4016,92 +5276,152 @@
       <c r="B29" s="9" t="n">
         <v>20260944</v>
       </c>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
+      <c r="C29" s="10" t="n">
+        <v>18411</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>18411</v>
+      </c>
       <c r="E29" s="11">
         <f>IF(OR(C29="",D29=""),"",D29-C29)</f>
         <v/>
       </c>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="10" t="n"/>
+      <c r="F29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H29" s="11">
         <f>IF(OR(F29="",G29=""),"",G29-F29)</f>
         <v/>
       </c>
-      <c r="I29" s="10" t="n"/>
-      <c r="J29" s="10" t="n"/>
+      <c r="I29" s="10" t="n">
+        <v>18206</v>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>18211</v>
+      </c>
       <c r="K29" s="11">
         <f>IF(OR(I29="",J29=""),"",J29-I29)</f>
         <v/>
       </c>
-      <c r="L29" s="10" t="n"/>
-      <c r="M29" s="10" t="n"/>
+      <c r="L29" s="10" t="n">
+        <v>18411</v>
+      </c>
+      <c r="M29" s="10" t="n">
+        <v>18411</v>
+      </c>
       <c r="N29" s="11">
         <f>IF(OR(L29="",M29=""),"",M29-L29)</f>
         <v/>
       </c>
-      <c r="O29" s="10" t="n"/>
-      <c r="P29" s="10" t="n"/>
+      <c r="O29" s="10" t="n">
+        <v>10.752208</v>
+      </c>
+      <c r="P29" s="10" t="n">
+        <v>7.241535</v>
+      </c>
       <c r="Q29" s="11">
         <f>IF(OR(O29="",P29=""),"",P29-O29)</f>
         <v/>
       </c>
-      <c r="R29" s="10" t="n"/>
-      <c r="S29" s="10" t="n"/>
+      <c r="R29" s="10" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="S29" s="10" t="n">
+        <v>17.7</v>
+      </c>
       <c r="T29" s="11">
         <f>IF(OR(R29="",S29=""),"",S29-R29)</f>
         <v/>
       </c>
-      <c r="U29" s="12" t="n"/>
-      <c r="V29" s="12" t="n"/>
+      <c r="U29" s="12" t="n">
+        <v>0.078594</v>
+      </c>
+      <c r="V29" s="12" t="n">
+        <v>0.018413</v>
+      </c>
       <c r="W29" s="13">
         <f>IF(OR(U29="",V29=""),"",V29-U29)</f>
         <v/>
       </c>
-      <c r="X29" s="10" t="n"/>
-      <c r="Y29" s="10" t="n"/>
+      <c r="X29" s="10" t="n">
+        <v>21.933933</v>
+      </c>
+      <c r="Y29" s="10" t="n">
+        <v>14.7616</v>
+      </c>
       <c r="Z29" s="11">
         <f>IF(OR(X29="",Y29=""),"",Y29-X29)</f>
         <v/>
       </c>
-      <c r="AA29" s="10" t="n"/>
-      <c r="AB29" s="10" t="n"/>
+      <c r="AA29" s="10" t="n">
+        <v>232</v>
+      </c>
+      <c r="AB29" s="10" t="n">
+        <v>169</v>
+      </c>
       <c r="AC29" s="11">
         <f>IF(OR(AA29="",AB29=""),"",AB29-AA29)</f>
         <v/>
       </c>
-      <c r="AD29" s="10" t="n"/>
-      <c r="AE29" s="10" t="n"/>
+      <c r="AD29" s="10" t="n">
+        <v>69.680786</v>
+      </c>
+      <c r="AE29" s="10" t="n">
+        <v>69.380786</v>
+      </c>
       <c r="AF29" s="11">
         <f>IF(OR(AD29="",AE29=""),"",AE29-AD29)</f>
         <v/>
       </c>
-      <c r="AG29" s="12" t="n"/>
-      <c r="AH29" s="12" t="n"/>
+      <c r="AG29" s="12" t="n">
+        <v>0.261165</v>
+      </c>
+      <c r="AH29" s="12" t="n">
+        <v>0.237425</v>
+      </c>
       <c r="AI29" s="13">
         <f>IF(OR(AG29="",AH29=""),"",AH29-AG29)</f>
         <v/>
       </c>
-      <c r="AJ29" s="12" t="n"/>
-      <c r="AK29" s="12" t="n"/>
+      <c r="AJ29" s="12" t="n">
+        <v>0.048473</v>
+      </c>
+      <c r="AK29" s="12" t="n">
+        <v>0.051708</v>
+      </c>
       <c r="AL29" s="13">
         <f>IF(OR(AJ29="",AK29=""),"",AK29-AJ29)</f>
         <v/>
       </c>
-      <c r="AM29" s="10" t="n"/>
-      <c r="AN29" s="10" t="n"/>
+      <c r="AM29" s="10" t="n">
+        <v>4365</v>
+      </c>
+      <c r="AN29" s="10" t="n">
+        <v>4365</v>
+      </c>
       <c r="AO29" s="11">
         <f>IF(OR(AM29="",AN29=""),"",AN29-AM29)</f>
         <v/>
       </c>
-      <c r="AP29" s="10" t="n"/>
-      <c r="AQ29" s="10" t="n"/>
+      <c r="AP29" s="10" t="n">
+        <v>16.177388</v>
+      </c>
+      <c r="AQ29" s="10" t="n">
+        <v>10.711065</v>
+      </c>
       <c r="AR29" s="11">
         <f>IF(OR(AP29="",AQ29=""),"",AQ29-AP29)</f>
         <v/>
       </c>
-      <c r="AS29" s="10" t="n"/>
-      <c r="AT29" s="10" t="n"/>
+      <c r="AS29" s="10" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="AT29" s="10" t="n">
+        <v>25.5</v>
+      </c>
       <c r="AU29" s="11">
         <f>IF(OR(AS29="",AT29=""),"",AT29-AS29)</f>
         <v/>
@@ -4114,92 +5434,152 @@
       <c r="B30" s="9" t="n">
         <v>20260945</v>
       </c>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
+      <c r="C30" s="10" t="n">
+        <v>18312</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>18312</v>
+      </c>
       <c r="E30" s="11">
         <f>IF(OR(C30="",D30=""),"",D30-C30)</f>
         <v/>
       </c>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
+      <c r="F30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H30" s="11">
         <f>IF(OR(F30="",G30=""),"",G30-F30)</f>
         <v/>
       </c>
-      <c r="I30" s="10" t="n"/>
-      <c r="J30" s="10" t="n"/>
+      <c r="I30" s="10" t="n">
+        <v>18104</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>18108</v>
+      </c>
       <c r="K30" s="11">
         <f>IF(OR(I30="",J30=""),"",J30-I30)</f>
         <v/>
       </c>
-      <c r="L30" s="10" t="n"/>
-      <c r="M30" s="10" t="n"/>
+      <c r="L30" s="10" t="n">
+        <v>18312</v>
+      </c>
+      <c r="M30" s="10" t="n">
+        <v>18312</v>
+      </c>
       <c r="N30" s="11">
         <f>IF(OR(L30="",M30=""),"",M30-L30)</f>
         <v/>
       </c>
-      <c r="O30" s="10" t="n"/>
-      <c r="P30" s="10" t="n"/>
+      <c r="O30" s="10" t="n">
+        <v>10.860436</v>
+      </c>
+      <c r="P30" s="10" t="n">
+        <v>7.422084</v>
+      </c>
       <c r="Q30" s="11">
         <f>IF(OR(O30="",P30=""),"",P30-O30)</f>
         <v/>
       </c>
-      <c r="R30" s="10" t="n"/>
-      <c r="S30" s="10" t="n"/>
+      <c r="R30" s="10" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="S30" s="10" t="n">
+        <v>18.6</v>
+      </c>
       <c r="T30" s="11">
         <f>IF(OR(R30="",S30=""),"",S30-R30)</f>
         <v/>
       </c>
-      <c r="U30" s="12" t="n"/>
-      <c r="V30" s="12" t="n"/>
+      <c r="U30" s="12" t="n">
+        <v>0.088139</v>
+      </c>
+      <c r="V30" s="12" t="n">
+        <v>0.02097</v>
+      </c>
       <c r="W30" s="13">
         <f>IF(OR(U30="",V30=""),"",V30-U30)</f>
         <v/>
       </c>
-      <c r="X30" s="10" t="n"/>
-      <c r="Y30" s="10" t="n"/>
+      <c r="X30" s="10" t="n">
+        <v>22.0427</v>
+      </c>
+      <c r="Y30" s="10" t="n">
+        <v>15.050167</v>
+      </c>
       <c r="Z30" s="11">
         <f>IF(OR(X30="",Y30=""),"",Y30-X30)</f>
         <v/>
       </c>
-      <c r="AA30" s="10" t="n"/>
-      <c r="AB30" s="10" t="n"/>
+      <c r="AA30" s="10" t="n">
+        <v>231</v>
+      </c>
+      <c r="AB30" s="10" t="n">
+        <v>170</v>
+      </c>
       <c r="AC30" s="11">
         <f>IF(OR(AA30="",AB30=""),"",AB30-AA30)</f>
         <v/>
       </c>
-      <c r="AD30" s="10" t="n"/>
-      <c r="AE30" s="10" t="n"/>
+      <c r="AD30" s="10" t="n">
+        <v>63.980786</v>
+      </c>
+      <c r="AE30" s="10" t="n">
+        <v>66.380786</v>
+      </c>
       <c r="AF30" s="11">
         <f>IF(OR(AD30="",AE30=""),"",AE30-AD30)</f>
         <v/>
       </c>
-      <c r="AG30" s="12" t="n"/>
-      <c r="AH30" s="12" t="n"/>
+      <c r="AG30" s="12" t="n">
+        <v>0.259297</v>
+      </c>
+      <c r="AH30" s="12" t="n">
+        <v>0.23577</v>
+      </c>
       <c r="AI30" s="13">
         <f>IF(OR(AG30="",AH30=""),"",AH30-AG30)</f>
         <v/>
       </c>
-      <c r="AJ30" s="12" t="n"/>
-      <c r="AK30" s="12" t="n"/>
+      <c r="AJ30" s="12" t="n">
+        <v>0.0465</v>
+      </c>
+      <c r="AK30" s="12" t="n">
+        <v>0.049754</v>
+      </c>
       <c r="AL30" s="13">
         <f>IF(OR(AJ30="",AK30=""),"",AK30-AJ30)</f>
         <v/>
       </c>
-      <c r="AM30" s="10" t="n"/>
-      <c r="AN30" s="10" t="n"/>
+      <c r="AM30" s="10" t="n">
+        <v>4355</v>
+      </c>
+      <c r="AN30" s="10" t="n">
+        <v>4355</v>
+      </c>
       <c r="AO30" s="11">
         <f>IF(OR(AM30="",AN30=""),"",AN30-AM30)</f>
         <v/>
       </c>
-      <c r="AP30" s="10" t="n"/>
-      <c r="AQ30" s="10" t="n"/>
+      <c r="AP30" s="10" t="n">
+        <v>15.935752</v>
+      </c>
+      <c r="AQ30" s="10" t="n">
+        <v>10.617382</v>
+      </c>
       <c r="AR30" s="11">
         <f>IF(OR(AP30="",AQ30=""),"",AQ30-AP30)</f>
         <v/>
       </c>
-      <c r="AS30" s="10" t="n"/>
-      <c r="AT30" s="10" t="n"/>
+      <c r="AS30" s="10" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="AT30" s="10" t="n">
+        <v>25.2</v>
+      </c>
       <c r="AU30" s="11">
         <f>IF(OR(AS30="",AT30=""),"",AT30-AS30)</f>
         <v/>
@@ -4212,92 +5592,152 @@
       <c r="B31" s="9" t="n">
         <v>20260946</v>
       </c>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="n"/>
+      <c r="C31" s="10" t="n">
+        <v>18491</v>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>18491</v>
+      </c>
       <c r="E31" s="11">
         <f>IF(OR(C31="",D31=""),"",D31-C31)</f>
         <v/>
       </c>
-      <c r="F31" s="10" t="n"/>
-      <c r="G31" s="10" t="n"/>
+      <c r="F31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H31" s="11">
         <f>IF(OR(F31="",G31=""),"",G31-F31)</f>
         <v/>
       </c>
-      <c r="I31" s="10" t="n"/>
-      <c r="J31" s="10" t="n"/>
+      <c r="I31" s="10" t="n">
+        <v>18268</v>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v>18277</v>
+      </c>
       <c r="K31" s="11">
         <f>IF(OR(I31="",J31=""),"",J31-I31)</f>
         <v/>
       </c>
-      <c r="L31" s="10" t="n"/>
-      <c r="M31" s="10" t="n"/>
+      <c r="L31" s="10" t="n">
+        <v>18491</v>
+      </c>
+      <c r="M31" s="10" t="n">
+        <v>18491</v>
+      </c>
       <c r="N31" s="11">
         <f>IF(OR(L31="",M31=""),"",M31-L31)</f>
         <v/>
       </c>
-      <c r="O31" s="10" t="n"/>
-      <c r="P31" s="10" t="n"/>
+      <c r="O31" s="10" t="n">
+        <v>11.350127</v>
+      </c>
+      <c r="P31" s="10" t="n">
+        <v>7.702217</v>
+      </c>
       <c r="Q31" s="11">
         <f>IF(OR(O31="",P31=""),"",P31-O31)</f>
         <v/>
       </c>
-      <c r="R31" s="10" t="n"/>
-      <c r="S31" s="10" t="n"/>
+      <c r="R31" s="10" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="S31" s="10" t="n">
+        <v>19.5</v>
+      </c>
       <c r="T31" s="11">
         <f>IF(OR(R31="",S31=""),"",S31-R31)</f>
         <v/>
       </c>
-      <c r="U31" s="12" t="n"/>
-      <c r="V31" s="12" t="n"/>
+      <c r="U31" s="12" t="n">
+        <v>0.09815599999999999</v>
+      </c>
+      <c r="V31" s="12" t="n">
+        <v>0.022876</v>
+      </c>
       <c r="W31" s="13">
         <f>IF(OR(U31="",V31=""),"",V31-U31)</f>
         <v/>
       </c>
-      <c r="X31" s="10" t="n"/>
-      <c r="Y31" s="10" t="n"/>
+      <c r="X31" s="10" t="n">
+        <v>23.2558</v>
+      </c>
+      <c r="Y31" s="10" t="n">
+        <v>15.750967</v>
+      </c>
       <c r="Z31" s="11">
         <f>IF(OR(X31="",Y31=""),"",Y31-X31)</f>
         <v/>
       </c>
-      <c r="AA31" s="10" t="n"/>
-      <c r="AB31" s="10" t="n"/>
+      <c r="AA31" s="10" t="n">
+        <v>213</v>
+      </c>
+      <c r="AB31" s="10" t="n">
+        <v>146</v>
+      </c>
       <c r="AC31" s="11">
         <f>IF(OR(AA31="",AB31=""),"",AB31-AA31)</f>
         <v/>
       </c>
-      <c r="AD31" s="10" t="n"/>
-      <c r="AE31" s="10" t="n"/>
+      <c r="AD31" s="10" t="n">
+        <v>65.48078599999999</v>
+      </c>
+      <c r="AE31" s="10" t="n">
+        <v>66.680786</v>
+      </c>
       <c r="AF31" s="11">
         <f>IF(OR(AD31="",AE31=""),"",AE31-AD31)</f>
         <v/>
       </c>
-      <c r="AG31" s="12" t="n"/>
-      <c r="AH31" s="12" t="n"/>
+      <c r="AG31" s="12" t="n">
+        <v>0.262022</v>
+      </c>
+      <c r="AH31" s="12" t="n">
+        <v>0.23818</v>
+      </c>
       <c r="AI31" s="13">
         <f>IF(OR(AG31="",AH31=""),"",AH31-AG31)</f>
         <v/>
       </c>
-      <c r="AJ31" s="12" t="n"/>
-      <c r="AK31" s="12" t="n"/>
+      <c r="AJ31" s="12" t="n">
+        <v>0.047761</v>
+      </c>
+      <c r="AK31" s="12" t="n">
+        <v>0.051747</v>
+      </c>
       <c r="AL31" s="13">
         <f>IF(OR(AJ31="",AK31=""),"",AK31-AJ31)</f>
         <v/>
       </c>
-      <c r="AM31" s="10" t="n"/>
-      <c r="AN31" s="10" t="n"/>
+      <c r="AM31" s="10" t="n">
+        <v>4371</v>
+      </c>
+      <c r="AN31" s="10" t="n">
+        <v>4371</v>
+      </c>
       <c r="AO31" s="11">
         <f>IF(OR(AM31="",AN31=""),"",AN31-AM31)</f>
         <v/>
       </c>
-      <c r="AP31" s="10" t="n"/>
-      <c r="AQ31" s="10" t="n"/>
+      <c r="AP31" s="10" t="n">
+        <v>16.489224</v>
+      </c>
+      <c r="AQ31" s="10" t="n">
+        <v>10.653123</v>
+      </c>
       <c r="AR31" s="11">
         <f>IF(OR(AP31="",AQ31=""),"",AQ31-AP31)</f>
         <v/>
       </c>
-      <c r="AS31" s="10" t="n"/>
-      <c r="AT31" s="10" t="n"/>
+      <c r="AS31" s="10" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="AT31" s="10" t="n">
+        <v>24.9</v>
+      </c>
       <c r="AU31" s="11">
         <f>IF(OR(AS31="",AT31=""),"",AT31-AS31)</f>
         <v/>
@@ -4310,92 +5750,152 @@
       <c r="B32" s="9" t="n">
         <v>20260947</v>
       </c>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
+      <c r="C32" s="10" t="n">
+        <v>18332</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>18332</v>
+      </c>
       <c r="E32" s="11">
         <f>IF(OR(C32="",D32=""),"",D32-C32)</f>
         <v/>
       </c>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="10" t="n"/>
+      <c r="F32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H32" s="11">
         <f>IF(OR(F32="",G32=""),"",G32-F32)</f>
         <v/>
       </c>
-      <c r="I32" s="10" t="n"/>
-      <c r="J32" s="10" t="n"/>
+      <c r="I32" s="10" t="n">
+        <v>18120</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>18117</v>
+      </c>
       <c r="K32" s="11">
         <f>IF(OR(I32="",J32=""),"",J32-I32)</f>
         <v/>
       </c>
-      <c r="L32" s="10" t="n"/>
-      <c r="M32" s="10" t="n"/>
+      <c r="L32" s="10" t="n">
+        <v>18332</v>
+      </c>
+      <c r="M32" s="10" t="n">
+        <v>18332</v>
+      </c>
       <c r="N32" s="11">
         <f>IF(OR(L32="",M32=""),"",M32-L32)</f>
         <v/>
       </c>
-      <c r="O32" s="10" t="n"/>
-      <c r="P32" s="10" t="n"/>
+      <c r="O32" s="10" t="n">
+        <v>10.995429</v>
+      </c>
+      <c r="P32" s="10" t="n">
+        <v>7.320412</v>
+      </c>
       <c r="Q32" s="11">
         <f>IF(OR(O32="",P32=""),"",P32-O32)</f>
         <v/>
       </c>
-      <c r="R32" s="10" t="n"/>
-      <c r="S32" s="10" t="n"/>
+      <c r="R32" s="10" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="S32" s="10" t="n">
+        <v>18.3</v>
+      </c>
       <c r="T32" s="11">
         <f>IF(OR(R32="",S32=""),"",S32-R32)</f>
         <v/>
       </c>
-      <c r="U32" s="12" t="n"/>
-      <c r="V32" s="12" t="n"/>
+      <c r="U32" s="12" t="n">
+        <v>0.085424</v>
+      </c>
+      <c r="V32" s="12" t="n">
+        <v>0.018656</v>
+      </c>
       <c r="W32" s="13">
         <f>IF(OR(U32="",V32=""),"",V32-U32)</f>
         <v/>
       </c>
-      <c r="X32" s="10" t="n"/>
-      <c r="Y32" s="10" t="n"/>
+      <c r="X32" s="10" t="n">
+        <v>22.3252</v>
+      </c>
+      <c r="Y32" s="10" t="n">
+        <v>14.852067</v>
+      </c>
       <c r="Z32" s="11">
         <f>IF(OR(X32="",Y32=""),"",Y32-X32)</f>
         <v/>
       </c>
-      <c r="AA32" s="10" t="n"/>
-      <c r="AB32" s="10" t="n"/>
+      <c r="AA32" s="10" t="n">
+        <v>231</v>
+      </c>
+      <c r="AB32" s="10" t="n">
+        <v>169</v>
+      </c>
       <c r="AC32" s="11">
         <f>IF(OR(AA32="",AB32=""),"",AB32-AA32)</f>
         <v/>
       </c>
-      <c r="AD32" s="10" t="n"/>
-      <c r="AE32" s="10" t="n"/>
+      <c r="AD32" s="10" t="n">
+        <v>66.080786</v>
+      </c>
+      <c r="AE32" s="10" t="n">
+        <v>64.880786</v>
+      </c>
       <c r="AF32" s="11">
         <f>IF(OR(AD32="",AE32=""),"",AE32-AD32)</f>
         <v/>
       </c>
-      <c r="AG32" s="12" t="n"/>
-      <c r="AH32" s="12" t="n"/>
+      <c r="AG32" s="12" t="n">
+        <v>0.259609</v>
+      </c>
+      <c r="AH32" s="12" t="n">
+        <v>0.236095</v>
+      </c>
       <c r="AI32" s="13">
         <f>IF(OR(AG32="",AH32=""),"",AH32-AG32)</f>
         <v/>
       </c>
-      <c r="AJ32" s="12" t="n"/>
-      <c r="AK32" s="12" t="n"/>
+      <c r="AJ32" s="12" t="n">
+        <v>0.046924</v>
+      </c>
+      <c r="AK32" s="12" t="n">
+        <v>0.050012</v>
+      </c>
       <c r="AL32" s="13">
         <f>IF(OR(AJ32="",AK32=""),"",AK32-AJ32)</f>
         <v/>
       </c>
-      <c r="AM32" s="10" t="n"/>
-      <c r="AN32" s="10" t="n"/>
+      <c r="AM32" s="10" t="n">
+        <v>4345</v>
+      </c>
+      <c r="AN32" s="10" t="n">
+        <v>4345</v>
+      </c>
       <c r="AO32" s="11">
         <f>IF(OR(AM32="",AN32=""),"",AN32-AM32)</f>
         <v/>
       </c>
-      <c r="AP32" s="10" t="n"/>
-      <c r="AQ32" s="10" t="n"/>
+      <c r="AP32" s="10" t="n">
+        <v>16.914753</v>
+      </c>
+      <c r="AQ32" s="10" t="n">
+        <v>10.820023</v>
+      </c>
       <c r="AR32" s="11">
         <f>IF(OR(AP32="",AQ32=""),"",AQ32-AP32)</f>
         <v/>
       </c>
-      <c r="AS32" s="10" t="n"/>
-      <c r="AT32" s="10" t="n"/>
+      <c r="AS32" s="10" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="AT32" s="10" t="n">
+        <v>25.5</v>
+      </c>
       <c r="AU32" s="11">
         <f>IF(OR(AS32="",AT32=""),"",AT32-AS32)</f>
         <v/>
@@ -4408,92 +5908,152 @@
       <c r="B33" s="9" t="n">
         <v>20260948</v>
       </c>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
+      <c r="C33" s="10" t="n">
+        <v>18364</v>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>18364</v>
+      </c>
       <c r="E33" s="11">
         <f>IF(OR(C33="",D33=""),"",D33-C33)</f>
         <v/>
       </c>
-      <c r="F33" s="10" t="n"/>
-      <c r="G33" s="10" t="n"/>
+      <c r="F33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H33" s="11">
         <f>IF(OR(F33="",G33=""),"",G33-F33)</f>
         <v/>
       </c>
-      <c r="I33" s="10" t="n"/>
-      <c r="J33" s="10" t="n"/>
+      <c r="I33" s="10" t="n">
+        <v>18157</v>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>18160</v>
+      </c>
       <c r="K33" s="11">
         <f>IF(OR(I33="",J33=""),"",J33-I33)</f>
         <v/>
       </c>
-      <c r="L33" s="10" t="n"/>
-      <c r="M33" s="10" t="n"/>
+      <c r="L33" s="10" t="n">
+        <v>18364</v>
+      </c>
+      <c r="M33" s="10" t="n">
+        <v>18364</v>
+      </c>
       <c r="N33" s="11">
         <f>IF(OR(L33="",M33=""),"",M33-L33)</f>
         <v/>
       </c>
-      <c r="O33" s="10" t="n"/>
-      <c r="P33" s="10" t="n"/>
+      <c r="O33" s="10" t="n">
+        <v>10.748067</v>
+      </c>
+      <c r="P33" s="10" t="n">
+        <v>7.21271</v>
+      </c>
       <c r="Q33" s="11">
         <f>IF(OR(O33="",P33=""),"",P33-O33)</f>
         <v/>
       </c>
-      <c r="R33" s="10" t="n"/>
-      <c r="S33" s="10" t="n"/>
+      <c r="R33" s="10" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="S33" s="10" t="n">
+        <v>17.7</v>
+      </c>
       <c r="T33" s="11">
         <f>IF(OR(R33="",S33=""),"",S33-R33)</f>
         <v/>
       </c>
-      <c r="U33" s="12" t="n"/>
-      <c r="V33" s="12" t="n"/>
+      <c r="U33" s="12" t="n">
+        <v>0.080429</v>
+      </c>
+      <c r="V33" s="12" t="n">
+        <v>0.01797</v>
+      </c>
       <c r="W33" s="13">
         <f>IF(OR(U33="",V33=""),"",V33-U33)</f>
         <v/>
       </c>
-      <c r="X33" s="10" t="n"/>
-      <c r="Y33" s="10" t="n"/>
+      <c r="X33" s="10" t="n">
+        <v>21.8718</v>
+      </c>
+      <c r="Y33" s="10" t="n">
+        <v>14.672433</v>
+      </c>
       <c r="Z33" s="11">
         <f>IF(OR(X33="",Y33=""),"",Y33-X33)</f>
         <v/>
       </c>
-      <c r="AA33" s="10" t="n"/>
-      <c r="AB33" s="10" t="n"/>
+      <c r="AA33" s="10" t="n">
+        <v>234</v>
+      </c>
+      <c r="AB33" s="10" t="n">
+        <v>167</v>
+      </c>
       <c r="AC33" s="11">
         <f>IF(OR(AA33="",AB33=""),"",AB33-AA33)</f>
         <v/>
       </c>
-      <c r="AD33" s="10" t="n"/>
-      <c r="AE33" s="10" t="n"/>
+      <c r="AD33" s="10" t="n">
+        <v>66.98078599999999</v>
+      </c>
+      <c r="AE33" s="10" t="n">
+        <v>66.680786</v>
+      </c>
       <c r="AF33" s="11">
         <f>IF(OR(AD33="",AE33=""),"",AE33-AD33)</f>
         <v/>
       </c>
-      <c r="AG33" s="12" t="n"/>
-      <c r="AH33" s="12" t="n"/>
+      <c r="AG33" s="12" t="n">
+        <v>0.259889</v>
+      </c>
+      <c r="AH33" s="12" t="n">
+        <v>0.23633</v>
+      </c>
       <c r="AI33" s="13">
         <f>IF(OR(AG33="",AH33=""),"",AH33-AG33)</f>
         <v/>
       </c>
-      <c r="AJ33" s="12" t="n"/>
-      <c r="AK33" s="12" t="n"/>
+      <c r="AJ33" s="12" t="n">
+        <v>0.04712</v>
+      </c>
+      <c r="AK33" s="12" t="n">
+        <v>0.051451</v>
+      </c>
       <c r="AL33" s="13">
         <f>IF(OR(AJ33="",AK33=""),"",AK33-AJ33)</f>
         <v/>
       </c>
-      <c r="AM33" s="10" t="n"/>
-      <c r="AN33" s="10" t="n"/>
+      <c r="AM33" s="10" t="n">
+        <v>4314</v>
+      </c>
+      <c r="AN33" s="10" t="n">
+        <v>4314</v>
+      </c>
       <c r="AO33" s="11">
         <f>IF(OR(AM33="",AN33=""),"",AN33-AM33)</f>
         <v/>
       </c>
-      <c r="AP33" s="10" t="n"/>
-      <c r="AQ33" s="10" t="n"/>
+      <c r="AP33" s="10" t="n">
+        <v>16.295063</v>
+      </c>
+      <c r="AQ33" s="10" t="n">
+        <v>10.424757</v>
+      </c>
       <c r="AR33" s="11">
         <f>IF(OR(AP33="",AQ33=""),"",AQ33-AP33)</f>
         <v/>
       </c>
-      <c r="AS33" s="10" t="n"/>
-      <c r="AT33" s="10" t="n"/>
+      <c r="AS33" s="10" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="AT33" s="10" t="n">
+        <v>24.6</v>
+      </c>
       <c r="AU33" s="11">
         <f>IF(OR(AS33="",AT33=""),"",AT33-AS33)</f>
         <v/>
@@ -4506,92 +6066,152 @@
       <c r="B34" s="9" t="n">
         <v>20260949</v>
       </c>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
+      <c r="C34" s="10" t="n">
+        <v>18389</v>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>18389</v>
+      </c>
       <c r="E34" s="11">
         <f>IF(OR(C34="",D34=""),"",D34-C34)</f>
         <v/>
       </c>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
+      <c r="F34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H34" s="11">
         <f>IF(OR(F34="",G34=""),"",G34-F34)</f>
         <v/>
       </c>
-      <c r="I34" s="10" t="n"/>
-      <c r="J34" s="10" t="n"/>
+      <c r="I34" s="10" t="n">
+        <v>18172</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v>18174</v>
+      </c>
       <c r="K34" s="11">
         <f>IF(OR(I34="",J34=""),"",J34-I34)</f>
         <v/>
       </c>
-      <c r="L34" s="10" t="n"/>
-      <c r="M34" s="10" t="n"/>
+      <c r="L34" s="10" t="n">
+        <v>18389</v>
+      </c>
+      <c r="M34" s="10" t="n">
+        <v>18389</v>
+      </c>
       <c r="N34" s="11">
         <f>IF(OR(L34="",M34=""),"",M34-L34)</f>
         <v/>
       </c>
-      <c r="O34" s="10" t="n"/>
-      <c r="P34" s="10" t="n"/>
+      <c r="O34" s="10" t="n">
+        <v>11.27244</v>
+      </c>
+      <c r="P34" s="10" t="n">
+        <v>7.702507</v>
+      </c>
       <c r="Q34" s="11">
         <f>IF(OR(O34="",P34=""),"",P34-O34)</f>
         <v/>
       </c>
-      <c r="R34" s="10" t="n"/>
-      <c r="S34" s="10" t="n"/>
+      <c r="R34" s="10" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="S34" s="10" t="n">
+        <v>19.2</v>
+      </c>
       <c r="T34" s="11">
         <f>IF(OR(R34="",S34=""),"",S34-R34)</f>
         <v/>
       </c>
-      <c r="U34" s="12" t="n"/>
-      <c r="V34" s="12" t="n"/>
+      <c r="U34" s="12" t="n">
+        <v>0.091957</v>
+      </c>
+      <c r="V34" s="12" t="n">
+        <v>0.024689</v>
+      </c>
       <c r="W34" s="13">
         <f>IF(OR(U34="",V34=""),"",V34-U34)</f>
         <v/>
       </c>
-      <c r="X34" s="10" t="n"/>
-      <c r="Y34" s="10" t="n"/>
+      <c r="X34" s="10" t="n">
+        <v>22.9735</v>
+      </c>
+      <c r="Y34" s="10" t="n">
+        <v>15.6903</v>
+      </c>
       <c r="Z34" s="11">
         <f>IF(OR(X34="",Y34=""),"",Y34-X34)</f>
         <v/>
       </c>
-      <c r="AA34" s="10" t="n"/>
-      <c r="AB34" s="10" t="n"/>
+      <c r="AA34" s="10" t="n">
+        <v>248</v>
+      </c>
+      <c r="AB34" s="10" t="n">
+        <v>200</v>
+      </c>
       <c r="AC34" s="11">
         <f>IF(OR(AA34="",AB34=""),"",AB34-AA34)</f>
         <v/>
       </c>
-      <c r="AD34" s="10" t="n"/>
-      <c r="AE34" s="10" t="n"/>
+      <c r="AD34" s="10" t="n">
+        <v>64.880786</v>
+      </c>
+      <c r="AE34" s="10" t="n">
+        <v>66.080786</v>
+      </c>
       <c r="AF34" s="11">
         <f>IF(OR(AD34="",AE34=""),"",AE34-AD34)</f>
         <v/>
       </c>
-      <c r="AG34" s="12" t="n"/>
-      <c r="AH34" s="12" t="n"/>
+      <c r="AG34" s="12" t="n">
+        <v>0.260555</v>
+      </c>
+      <c r="AH34" s="12" t="n">
+        <v>0.236949</v>
+      </c>
       <c r="AI34" s="13">
         <f>IF(OR(AG34="",AH34=""),"",AH34-AG34)</f>
         <v/>
       </c>
-      <c r="AJ34" s="12" t="n"/>
-      <c r="AK34" s="12" t="n"/>
+      <c r="AJ34" s="12" t="n">
+        <v>0.04606</v>
+      </c>
+      <c r="AK34" s="12" t="n">
+        <v>0.050548</v>
+      </c>
       <c r="AL34" s="13">
         <f>IF(OR(AJ34="",AK34=""),"",AK34-AJ34)</f>
         <v/>
       </c>
-      <c r="AM34" s="10" t="n"/>
-      <c r="AN34" s="10" t="n"/>
+      <c r="AM34" s="10" t="n">
+        <v>4349</v>
+      </c>
+      <c r="AN34" s="10" t="n">
+        <v>4349</v>
+      </c>
       <c r="AO34" s="11">
         <f>IF(OR(AM34="",AN34=""),"",AN34-AM34)</f>
         <v/>
       </c>
-      <c r="AP34" s="10" t="n"/>
-      <c r="AQ34" s="10" t="n"/>
+      <c r="AP34" s="10" t="n">
+        <v>16.607473</v>
+      </c>
+      <c r="AQ34" s="10" t="n">
+        <v>11.372269</v>
+      </c>
       <c r="AR34" s="11">
         <f>IF(OR(AP34="",AQ34=""),"",AQ34-AP34)</f>
         <v/>
       </c>
-      <c r="AS34" s="10" t="n"/>
-      <c r="AT34" s="10" t="n"/>
+      <c r="AS34" s="10" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="AT34" s="10" t="n">
+        <v>27</v>
+      </c>
       <c r="AU34" s="11">
         <f>IF(OR(AS34="",AT34=""),"",AT34-AS34)</f>
         <v/>
@@ -4604,92 +6224,152 @@
       <c r="B35" s="9" t="n">
         <v>20260950</v>
       </c>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
+      <c r="C35" s="10" t="n">
+        <v>18432</v>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>18432</v>
+      </c>
       <c r="E35" s="11">
         <f>IF(OR(C35="",D35=""),"",D35-C35)</f>
         <v/>
       </c>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="10" t="n"/>
+      <c r="F35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H35" s="11">
         <f>IF(OR(F35="",G35=""),"",G35-F35)</f>
         <v/>
       </c>
-      <c r="I35" s="10" t="n"/>
-      <c r="J35" s="10" t="n"/>
+      <c r="I35" s="10" t="n">
+        <v>18220</v>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v>18220</v>
+      </c>
       <c r="K35" s="11">
         <f>IF(OR(I35="",J35=""),"",J35-I35)</f>
         <v/>
       </c>
-      <c r="L35" s="10" t="n"/>
-      <c r="M35" s="10" t="n"/>
+      <c r="L35" s="10" t="n">
+        <v>18432</v>
+      </c>
+      <c r="M35" s="10" t="n">
+        <v>18432</v>
+      </c>
       <c r="N35" s="11">
         <f>IF(OR(L35="",M35=""),"",M35-L35)</f>
         <v/>
       </c>
-      <c r="O35" s="10" t="n"/>
-      <c r="P35" s="10" t="n"/>
+      <c r="O35" s="10" t="n">
+        <v>11.007064</v>
+      </c>
+      <c r="P35" s="10" t="n">
+        <v>7.4736</v>
+      </c>
       <c r="Q35" s="11">
         <f>IF(OR(O35="",P35=""),"",P35-O35)</f>
         <v/>
       </c>
-      <c r="R35" s="10" t="n"/>
-      <c r="S35" s="10" t="n"/>
+      <c r="R35" s="10" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="S35" s="10" t="n">
+        <v>18.6</v>
+      </c>
       <c r="T35" s="11">
         <f>IF(OR(R35="",S35=""),"",S35-R35)</f>
         <v/>
       </c>
-      <c r="U35" s="12" t="n"/>
-      <c r="V35" s="12" t="n"/>
+      <c r="U35" s="12" t="n">
+        <v>0.085775</v>
+      </c>
+      <c r="V35" s="12" t="n">
+        <v>0.021484</v>
+      </c>
       <c r="W35" s="13">
         <f>IF(OR(U35="",V35=""),"",V35-U35)</f>
         <v/>
       </c>
-      <c r="X35" s="10" t="n"/>
-      <c r="Y35" s="10" t="n"/>
+      <c r="X35" s="10" t="n">
+        <v>22.483567</v>
+      </c>
+      <c r="Y35" s="10" t="n">
+        <v>15.2547</v>
+      </c>
       <c r="Z35" s="11">
         <f>IF(OR(X35="",Y35=""),"",Y35-X35)</f>
         <v/>
       </c>
-      <c r="AA35" s="10" t="n"/>
-      <c r="AB35" s="10" t="n"/>
+      <c r="AA35" s="10" t="n">
+        <v>241</v>
+      </c>
+      <c r="AB35" s="10" t="n">
+        <v>181</v>
+      </c>
       <c r="AC35" s="11">
         <f>IF(OR(AA35="",AB35=""),"",AB35-AA35)</f>
         <v/>
       </c>
-      <c r="AD35" s="10" t="n"/>
-      <c r="AE35" s="10" t="n"/>
+      <c r="AD35" s="10" t="n">
+        <v>64.580786</v>
+      </c>
+      <c r="AE35" s="10" t="n">
+        <v>64.580786</v>
+      </c>
       <c r="AF35" s="11">
         <f>IF(OR(AD35="",AE35=""),"",AE35-AD35)</f>
         <v/>
       </c>
-      <c r="AG35" s="12" t="n"/>
-      <c r="AH35" s="12" t="n"/>
+      <c r="AG35" s="12" t="n">
+        <v>0.261349</v>
+      </c>
+      <c r="AH35" s="12" t="n">
+        <v>0.237619</v>
+      </c>
       <c r="AI35" s="13">
         <f>IF(OR(AG35="",AH35=""),"",AH35-AG35)</f>
         <v/>
       </c>
-      <c r="AJ35" s="12" t="n"/>
-      <c r="AK35" s="12" t="n"/>
+      <c r="AJ35" s="12" t="n">
+        <v>0.047015</v>
+      </c>
+      <c r="AK35" s="12" t="n">
+        <v>0.050772</v>
+      </c>
       <c r="AL35" s="13">
         <f>IF(OR(AJ35="",AK35=""),"",AK35-AJ35)</f>
         <v/>
       </c>
-      <c r="AM35" s="10" t="n"/>
-      <c r="AN35" s="10" t="n"/>
+      <c r="AM35" s="10" t="n">
+        <v>4373</v>
+      </c>
+      <c r="AN35" s="10" t="n">
+        <v>4373</v>
+      </c>
       <c r="AO35" s="11">
         <f>IF(OR(AM35="",AN35=""),"",AN35-AM35)</f>
         <v/>
       </c>
-      <c r="AP35" s="10" t="n"/>
-      <c r="AQ35" s="10" t="n"/>
+      <c r="AP35" s="10" t="n">
+        <v>16.705397</v>
+      </c>
+      <c r="AQ35" s="10" t="n">
+        <v>10.988452</v>
+      </c>
       <c r="AR35" s="11">
         <f>IF(OR(AP35="",AQ35=""),"",AQ35-AP35)</f>
         <v/>
       </c>
-      <c r="AS35" s="10" t="n"/>
-      <c r="AT35" s="10" t="n"/>
+      <c r="AS35" s="10" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="AT35" s="10" t="n">
+        <v>25.8</v>
+      </c>
       <c r="AU35" s="11">
         <f>IF(OR(AS35="",AT35=""),"",AT35-AS35)</f>
         <v/>
@@ -4702,92 +6382,152 @@
       <c r="B36" s="9" t="n">
         <v>20260951</v>
       </c>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
+      <c r="C36" s="10" t="n">
+        <v>18420</v>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>18420</v>
+      </c>
       <c r="E36" s="11">
         <f>IF(OR(C36="",D36=""),"",D36-C36)</f>
         <v/>
       </c>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="10" t="n"/>
+      <c r="F36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H36" s="11">
         <f>IF(OR(F36="",G36=""),"",G36-F36)</f>
         <v/>
       </c>
-      <c r="I36" s="10" t="n"/>
-      <c r="J36" s="10" t="n"/>
+      <c r="I36" s="10" t="n">
+        <v>18214</v>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>18214</v>
+      </c>
       <c r="K36" s="11">
         <f>IF(OR(I36="",J36=""),"",J36-I36)</f>
         <v/>
       </c>
-      <c r="L36" s="10" t="n"/>
-      <c r="M36" s="10" t="n"/>
+      <c r="L36" s="10" t="n">
+        <v>18420</v>
+      </c>
+      <c r="M36" s="10" t="n">
+        <v>18420</v>
+      </c>
       <c r="N36" s="11">
         <f>IF(OR(L36="",M36=""),"",M36-L36)</f>
         <v/>
       </c>
-      <c r="O36" s="10" t="n"/>
-      <c r="P36" s="10" t="n"/>
+      <c r="O36" s="10" t="n">
+        <v>10.703518</v>
+      </c>
+      <c r="P36" s="10" t="n">
+        <v>7.300505</v>
+      </c>
       <c r="Q36" s="11">
         <f>IF(OR(O36="",P36=""),"",P36-O36)</f>
         <v/>
       </c>
-      <c r="R36" s="10" t="n"/>
-      <c r="S36" s="10" t="n"/>
+      <c r="R36" s="10" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="S36" s="10" t="n">
+        <v>18</v>
+      </c>
       <c r="T36" s="11">
         <f>IF(OR(R36="",S36=""),"",S36-R36)</f>
         <v/>
       </c>
-      <c r="U36" s="12" t="n"/>
-      <c r="V36" s="12" t="n"/>
+      <c r="U36" s="12" t="n">
+        <v>0.079262</v>
+      </c>
+      <c r="V36" s="12" t="n">
+        <v>0.020358</v>
+      </c>
       <c r="W36" s="13">
         <f>IF(OR(U36="",V36=""),"",V36-U36)</f>
         <v/>
       </c>
-      <c r="X36" s="10" t="n"/>
-      <c r="Y36" s="10" t="n"/>
+      <c r="X36" s="10" t="n">
+        <v>21.835767</v>
+      </c>
+      <c r="Y36" s="10" t="n">
+        <v>14.8736</v>
+      </c>
       <c r="Z36" s="11">
         <f>IF(OR(X36="",Y36=""),"",Y36-X36)</f>
         <v/>
       </c>
-      <c r="AA36" s="10" t="n"/>
-      <c r="AB36" s="10" t="n"/>
+      <c r="AA36" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB36" s="10" t="n">
+        <v>176</v>
+      </c>
       <c r="AC36" s="11">
         <f>IF(OR(AA36="",AB36=""),"",AB36-AA36)</f>
         <v/>
       </c>
-      <c r="AD36" s="10" t="n"/>
-      <c r="AE36" s="10" t="n"/>
+      <c r="AD36" s="10" t="n">
+        <v>65.76373700000001</v>
+      </c>
+      <c r="AE36" s="10" t="n">
+        <v>63.663737</v>
+      </c>
       <c r="AF36" s="11">
         <f>IF(OR(AD36="",AE36=""),"",AE36-AD36)</f>
         <v/>
       </c>
-      <c r="AG36" s="12" t="n"/>
-      <c r="AH36" s="12" t="n"/>
+      <c r="AG36" s="12" t="n">
+        <v>0.260637</v>
+      </c>
+      <c r="AH36" s="12" t="n">
+        <v>0.236943</v>
+      </c>
       <c r="AI36" s="13">
         <f>IF(OR(AG36="",AH36=""),"",AH36-AG36)</f>
         <v/>
       </c>
-      <c r="AJ36" s="12" t="n"/>
-      <c r="AK36" s="12" t="n"/>
+      <c r="AJ36" s="12" t="n">
+        <v>0.047434</v>
+      </c>
+      <c r="AK36" s="12" t="n">
+        <v>0.051357</v>
+      </c>
       <c r="AL36" s="13">
         <f>IF(OR(AJ36="",AK36=""),"",AK36-AJ36)</f>
         <v/>
       </c>
-      <c r="AM36" s="10" t="n"/>
-      <c r="AN36" s="10" t="n"/>
+      <c r="AM36" s="10" t="n">
+        <v>4368</v>
+      </c>
+      <c r="AN36" s="10" t="n">
+        <v>4368</v>
+      </c>
       <c r="AO36" s="11">
         <f>IF(OR(AM36="",AN36=""),"",AN36-AM36)</f>
         <v/>
       </c>
-      <c r="AP36" s="10" t="n"/>
-      <c r="AQ36" s="10" t="n"/>
+      <c r="AP36" s="10" t="n">
+        <v>15.945536</v>
+      </c>
+      <c r="AQ36" s="10" t="n">
+        <v>10.528159</v>
+      </c>
       <c r="AR36" s="11">
         <f>IF(OR(AP36="",AQ36=""),"",AQ36-AP36)</f>
         <v/>
       </c>
-      <c r="AS36" s="10" t="n"/>
-      <c r="AT36" s="10" t="n"/>
+      <c r="AS36" s="10" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="AT36" s="10" t="n">
+        <v>24.9</v>
+      </c>
       <c r="AU36" s="11">
         <f>IF(OR(AS36="",AT36=""),"",AT36-AS36)</f>
         <v/>
@@ -4800,92 +6540,152 @@
       <c r="B37" s="9" t="n">
         <v>20260952</v>
       </c>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="n"/>
+      <c r="C37" s="10" t="n">
+        <v>18383</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>18383</v>
+      </c>
       <c r="E37" s="11">
         <f>IF(OR(C37="",D37=""),"",D37-C37)</f>
         <v/>
       </c>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="10" t="n"/>
+      <c r="F37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H37" s="11">
         <f>IF(OR(F37="",G37=""),"",G37-F37)</f>
         <v/>
       </c>
-      <c r="I37" s="10" t="n"/>
-      <c r="J37" s="10" t="n"/>
+      <c r="I37" s="10" t="n">
+        <v>18186</v>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>18182</v>
+      </c>
       <c r="K37" s="11">
         <f>IF(OR(I37="",J37=""),"",J37-I37)</f>
         <v/>
       </c>
-      <c r="L37" s="10" t="n"/>
-      <c r="M37" s="10" t="n"/>
+      <c r="L37" s="10" t="n">
+        <v>18383</v>
+      </c>
+      <c r="M37" s="10" t="n">
+        <v>18383</v>
+      </c>
       <c r="N37" s="11">
         <f>IF(OR(L37="",M37=""),"",M37-L37)</f>
         <v/>
       </c>
-      <c r="O37" s="10" t="n"/>
-      <c r="P37" s="10" t="n"/>
+      <c r="O37" s="10" t="n">
+        <v>10.39722</v>
+      </c>
+      <c r="P37" s="10" t="n">
+        <v>7.268607</v>
+      </c>
       <c r="Q37" s="11">
         <f>IF(OR(O37="",P37=""),"",P37-O37)</f>
         <v/>
       </c>
-      <c r="R37" s="10" t="n"/>
-      <c r="S37" s="10" t="n"/>
+      <c r="R37" s="10" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="S37" s="10" t="n">
+        <v>18.3</v>
+      </c>
       <c r="T37" s="11">
         <f>IF(OR(R37="",S37=""),"",S37-R37)</f>
         <v/>
       </c>
-      <c r="U37" s="12" t="n"/>
-      <c r="V37" s="12" t="n"/>
+      <c r="U37" s="12" t="n">
+        <v>0.07593999999999999</v>
+      </c>
+      <c r="V37" s="12" t="n">
+        <v>0.015123</v>
+      </c>
       <c r="W37" s="13">
         <f>IF(OR(U37="",V37=""),"",V37-U37)</f>
         <v/>
       </c>
-      <c r="X37" s="10" t="n"/>
-      <c r="Y37" s="10" t="n"/>
+      <c r="X37" s="10" t="n">
+        <v>21.1824</v>
+      </c>
+      <c r="Y37" s="10" t="n">
+        <v>14.802633</v>
+      </c>
       <c r="Z37" s="11">
         <f>IF(OR(X37="",Y37=""),"",Y37-X37)</f>
         <v/>
       </c>
-      <c r="AA37" s="10" t="n"/>
-      <c r="AB37" s="10" t="n"/>
+      <c r="AA37" s="10" t="n">
+        <v>217</v>
+      </c>
+      <c r="AB37" s="10" t="n">
+        <v>160</v>
+      </c>
       <c r="AC37" s="11">
         <f>IF(OR(AA37="",AB37=""),"",AB37-AA37)</f>
         <v/>
       </c>
-      <c r="AD37" s="10" t="n"/>
-      <c r="AE37" s="10" t="n"/>
+      <c r="AD37" s="10" t="n">
+        <v>65.78078600000001</v>
+      </c>
+      <c r="AE37" s="10" t="n">
+        <v>65.78078600000001</v>
+      </c>
       <c r="AF37" s="11">
         <f>IF(OR(AD37="",AE37=""),"",AE37-AD37)</f>
         <v/>
       </c>
-      <c r="AG37" s="12" t="n"/>
-      <c r="AH37" s="12" t="n"/>
+      <c r="AG37" s="12" t="n">
+        <v>0.260454</v>
+      </c>
+      <c r="AH37" s="12" t="n">
+        <v>0.236773</v>
+      </c>
       <c r="AI37" s="13">
         <f>IF(OR(AG37="",AH37=""),"",AH37-AG37)</f>
         <v/>
       </c>
-      <c r="AJ37" s="12" t="n"/>
-      <c r="AK37" s="12" t="n"/>
+      <c r="AJ37" s="12" t="n">
+        <v>0.04749</v>
+      </c>
+      <c r="AK37" s="12" t="n">
+        <v>0.052111</v>
+      </c>
       <c r="AL37" s="13">
         <f>IF(OR(AJ37="",AK37=""),"",AK37-AJ37)</f>
         <v/>
       </c>
-      <c r="AM37" s="10" t="n"/>
-      <c r="AN37" s="10" t="n"/>
+      <c r="AM37" s="10" t="n">
+        <v>4333</v>
+      </c>
+      <c r="AN37" s="10" t="n">
+        <v>4333</v>
+      </c>
       <c r="AO37" s="11">
         <f>IF(OR(AM37="",AN37=""),"",AN37-AM37)</f>
         <v/>
       </c>
-      <c r="AP37" s="10" t="n"/>
-      <c r="AQ37" s="10" t="n"/>
+      <c r="AP37" s="10" t="n">
+        <v>15.237688</v>
+      </c>
+      <c r="AQ37" s="10" t="n">
+        <v>10.441426</v>
+      </c>
       <c r="AR37" s="11">
         <f>IF(OR(AP37="",AQ37=""),"",AQ37-AP37)</f>
         <v/>
       </c>
-      <c r="AS37" s="10" t="n"/>
-      <c r="AT37" s="10" t="n"/>
+      <c r="AS37" s="10" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="AT37" s="10" t="n">
+        <v>24.6</v>
+      </c>
       <c r="AU37" s="11">
         <f>IF(OR(AS37="",AT37=""),"",AT37-AS37)</f>
         <v/>
@@ -7831,6 +9631,7 @@
         <v/>
       </c>
     </row>
+    <row r="68"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
